--- a/Historical Data.xlsx
+++ b/Historical Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ex0164\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CED636F-2508-4576-BAD9-D50477BC05B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02805BF9-C8A8-4542-8579-74494461A139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{0D7B3432-4E03-4EA4-BD9E-FF20B9F42EA8}"/>
   </bookViews>
@@ -17,6 +17,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="77">
   <si>
     <t>S11434-002A0X</t>
   </si>
@@ -269,6 +270,9 @@
   <si>
     <t>S11398-030A0X</t>
   </si>
+  <si>
+    <t>Color</t>
+  </si>
 </sst>
 </file>
 
@@ -392,727 +396,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="194">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="122">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6423,6 +5707,3535 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Summery sheet"/>
+      <sheetName val="MP-01"/>
+      <sheetName val="MP-07"/>
+      <sheetName val="MP-15"/>
+      <sheetName val="MP-17"/>
+      <sheetName val="MP-14"/>
+      <sheetName val="MP-03"/>
+      <sheetName val="MP-04"/>
+      <sheetName val="MP-11"/>
+      <sheetName val="MP-12"/>
+      <sheetName val="MP-16"/>
+      <sheetName val="MP-10"/>
+      <sheetName val="MP-09"/>
+      <sheetName val="MP-08"/>
+      <sheetName val="MP-05"/>
+      <sheetName val="MP-13"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>Part No.</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>Description</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>Machine No.</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>PLAN</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>Machine by DATA</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>Color</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>14SW030081-00001X0</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>COUPLER GUIDE</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E2">
+            <v>895.25806451612902</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>S11434-002A0X</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>INSULATOR CP LIGHT RH</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E3">
+            <v>563.51612903225805</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>S41354-011A0X</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E4">
+            <v>1768.8387096774195</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>S21114-005A0X</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>INSULATOR CP.</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E5" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F5" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>S21077-008A0X</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E6" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F6" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>S12094-003A0X</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>INSULATOR CP. TURN, DIMMER &amp; LIGHT RH</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E7">
+            <v>15.677419354838708</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>S12071-001A0X</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>Ins. CP Turn. Dimmer &amp; Light LH</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E8">
+            <v>31.354838709677416</v>
+          </cell>
+          <cell r="F8" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>S21028-002A0X</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>Insulator</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E9" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F9" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>S12113-001A0X</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>INSULATOR CP TURN DIMMER &amp; LIGHT LH</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E10">
+            <v>3.67741935483871</v>
+          </cell>
+          <cell r="F10" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G10" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>S21021-012A0X</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>Insulator Cp</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>M.P-01</v>
+          </cell>
+          <cell r="E11">
+            <v>604.0645161290322</v>
+          </cell>
+          <cell r="F11" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>S31841-008A0X</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>PIN HEADER</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E12">
+            <v>745.64516129032268</v>
+          </cell>
+          <cell r="F12" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>S31867-002A0X</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E13">
+            <v>762.87096774193549</v>
+          </cell>
+          <cell r="F13" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G13" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>S31838-004A0X</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E14">
+            <v>183.87096774193549</v>
+          </cell>
+          <cell r="F14" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>S31842-004A0X</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E15">
+            <v>86.516129032258064</v>
+          </cell>
+          <cell r="F15" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>S31839-004A0X</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E16">
+            <v>190.64516129032256</v>
+          </cell>
+          <cell r="F16" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>S22166-013A0X</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>HOLDER INTR CP</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E17">
+            <v>248.0322580645161</v>
+          </cell>
+          <cell r="F17" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G17" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>S41222-022</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E18" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F18" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G18" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>M41035-032A0X</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E19" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F19" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G19" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>14SW311082-00006X0</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>HOLDER, CP</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E20">
+            <v>6125.4193548387093</v>
+          </cell>
+          <cell r="F20" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>S31741-005A0X</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E21">
+            <v>5535.5806451612907</v>
+          </cell>
+          <cell r="F21" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>14SW311144-00003X0</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E22">
+            <v>534</v>
+          </cell>
+          <cell r="F22" t="str">
+            <v>INJ.MOULD. M/C JSW-55T</v>
+          </cell>
+          <cell r="G22" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>S31868-005A0X</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E23">
+            <v>53.612903225806448</v>
+          </cell>
+          <cell r="F23" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G23" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>14SW311038-00005X0</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E24">
+            <v>1178.7096774193546</v>
+          </cell>
+          <cell r="F24" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G24" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>14SW410464-00009X0</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>PIN HEADER</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>M.P-03</v>
+          </cell>
+          <cell r="E25">
+            <v>1870.2580645161288</v>
+          </cell>
+          <cell r="F25" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G25" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>S11398-016A0X</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>HOLDER CP CONTACT DIM &amp; WASH</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E26">
+            <v>1383.0967741935485</v>
+          </cell>
+          <cell r="F26" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G26" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>S11398-017A0X</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>HOLDER CP CONTACT LIGHT</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E27">
+            <v>693.48387096774195</v>
+          </cell>
+          <cell r="F27" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G27" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>14SW311082-00006X0</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>HOLDER, CP</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E28">
+            <v>6125.4193548387093</v>
+          </cell>
+          <cell r="F28" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G28" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>14SW210274-00013X0</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>CONTACT CP</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E29">
+            <v>7373.2258064516118</v>
+          </cell>
+          <cell r="F29" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G29" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>S41356-021A0X</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>CONNECTOR CP</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E30">
+            <v>368.32258064516134</v>
+          </cell>
+          <cell r="F30" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G30" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>14SW210274-00016X0</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>INSULATOR CP, AUTO</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E31">
+            <v>7373.2258064516118</v>
+          </cell>
+          <cell r="F31" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G31" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>S21028-002A0X</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>Insulator</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G32" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>14SW311011-00003X0</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E33">
+            <v>1276.258064516129</v>
+          </cell>
+          <cell r="F33" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G33" t="str">
+            <v>Blue</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>S22085-002</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>Insulator</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E34" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F34" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G34" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>S33105-017A0X</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>TERMINAL COMP</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E35">
+            <v>4302</v>
+          </cell>
+          <cell r="F35" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G35" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>S32073-012A0X</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>Ter. Guide</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E36">
+            <v>522.58064516129025</v>
+          </cell>
+          <cell r="F36" t="str">
+            <v>INJ.MOULD. M/C(YUDEK)V</v>
+          </cell>
+          <cell r="G36" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>14SW311101-00003X0</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>M.P-04</v>
+          </cell>
+          <cell r="E37">
+            <v>730.9354838709678</v>
+          </cell>
+          <cell r="F37" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G37" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>14SW030082-00001X0</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>M.P-05</v>
+          </cell>
+          <cell r="E38">
+            <v>479.70967741935488</v>
+          </cell>
+          <cell r="F38" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G38" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>S13083-003A0X</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>INSULATOR CP WIPER LH</v>
+          </cell>
+          <cell r="D39" t="str">
+            <v>M.P-05</v>
+          </cell>
+          <cell r="E39">
+            <v>2579.6129032258063</v>
+          </cell>
+          <cell r="F39" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G39" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>S12095-004A0X</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>INSULATOR CP,TURN DIMMER &amp; LIGHT,LH</v>
+          </cell>
+          <cell r="D40" t="str">
+            <v>M.P-05</v>
+          </cell>
+          <cell r="E40">
+            <v>1420.258064516129</v>
+          </cell>
+          <cell r="F40" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G40" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>S22063-003A0X</v>
+          </cell>
+          <cell r="C41" t="str">
+            <v>Insulator CP</v>
+          </cell>
+          <cell r="D41" t="str">
+            <v>M.P-05</v>
+          </cell>
+          <cell r="E41" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F41" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G41" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>S13108-002A0X</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>INSULATOR. CP WIPER RH</v>
+          </cell>
+          <cell r="D42" t="str">
+            <v>M.P-05</v>
+          </cell>
+          <cell r="E42">
+            <v>15621.096774193549</v>
+          </cell>
+          <cell r="F42" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G42" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>14SW220197-00005X0</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>CONNECTOR CP</v>
+          </cell>
+          <cell r="D43" t="str">
+            <v>M.P-05</v>
+          </cell>
+          <cell r="E43">
+            <v>2359.8387096774195</v>
+          </cell>
+          <cell r="F43" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G43" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>S31437-004A0X</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D44" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E44">
+            <v>6278.6129032258068</v>
+          </cell>
+          <cell r="F44" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G44" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45" t="str">
+            <v>S12095-003A0X</v>
+          </cell>
+          <cell r="C45" t="str">
+            <v>CONTACT CP, DIMMER, LH</v>
+          </cell>
+          <cell r="D45" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E45">
+            <v>2537.2258064516127</v>
+          </cell>
+          <cell r="F45" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G45" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46" t="str">
+            <v>S12095-011A0X</v>
+          </cell>
+          <cell r="C46" t="str">
+            <v>CONTACT CP, LIGHT</v>
+          </cell>
+          <cell r="D46" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E46">
+            <v>2131.8387096774195</v>
+          </cell>
+          <cell r="F46" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G46" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47" t="str">
+            <v>S31842-004A0X</v>
+          </cell>
+          <cell r="C47" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D47" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E47">
+            <v>86.516129032258064</v>
+          </cell>
+          <cell r="F47" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G47" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48" t="str">
+            <v>S13123-002A0X</v>
+          </cell>
+          <cell r="C48" t="str">
+            <v>INSULATOR CP RR WIPER LH</v>
+          </cell>
+          <cell r="D48" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E48">
+            <v>499.45161290322574</v>
+          </cell>
+          <cell r="F48" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G48" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49" t="str">
+            <v>S13112-006A0X</v>
+          </cell>
+          <cell r="C49" t="str">
+            <v>INSULATOR CP, RR WIPER, RH</v>
+          </cell>
+          <cell r="D49" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E49">
+            <v>2805.483870967742</v>
+          </cell>
+          <cell r="F49" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G49" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50" t="str">
+            <v>S13052-005A0X</v>
+          </cell>
+          <cell r="C50" t="str">
+            <v>CONTACT CP.RR.WI</v>
+          </cell>
+          <cell r="D50" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E50">
+            <v>488.80645161290323</v>
+          </cell>
+          <cell r="F50" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G50" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51" t="str">
+            <v>S13083-011A0X</v>
+          </cell>
+          <cell r="C51" t="str">
+            <v>INSULATOR CP,RR WIPER,LH</v>
+          </cell>
+          <cell r="D51" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E51">
+            <v>1594.0645161290322</v>
+          </cell>
+          <cell r="F51" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G51" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52" t="str">
+            <v>14SW220197-00010X0</v>
+          </cell>
+          <cell r="C52" t="str">
+            <v>PIN HEADER</v>
+          </cell>
+          <cell r="D52" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E52">
+            <v>2359.8387096774195</v>
+          </cell>
+          <cell r="F52" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G52" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53" t="str">
+            <v>14SW311082-00006X0</v>
+          </cell>
+          <cell r="C53" t="str">
+            <v>HOLDER, CP</v>
+          </cell>
+          <cell r="D53" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E53">
+            <v>6125.4193548387093</v>
+          </cell>
+          <cell r="F53" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G53" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54" t="str">
+            <v>S12091-001A0X</v>
+          </cell>
+          <cell r="C54" t="str">
+            <v>INSULATOR CP, FOG, LH</v>
+          </cell>
+          <cell r="D54" t="str">
+            <v>M.P-07</v>
+          </cell>
+          <cell r="E54">
+            <v>277.25806451612902</v>
+          </cell>
+          <cell r="F54" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G54" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55" t="str">
+            <v>14SW311155-00003X0</v>
+          </cell>
+          <cell r="C55" t="str">
+            <v>INSULATOR</v>
+          </cell>
+          <cell r="D55" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E55">
+            <v>1770.6774193548388</v>
+          </cell>
+          <cell r="F55" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G55" t="str">
+            <v>Blue</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56" t="str">
+            <v>S03066-008A0X</v>
+          </cell>
+          <cell r="C56" t="str">
+            <v>COUPLER GUIDE 4P</v>
+          </cell>
+          <cell r="D56" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E56">
+            <v>105.29032258064515</v>
+          </cell>
+          <cell r="F56" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G56" t="str">
+            <v>Blue</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57" t="str">
+            <v>S31867-002A0X</v>
+          </cell>
+          <cell r="C57" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D57" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E57">
+            <v>762.87096774193549</v>
+          </cell>
+          <cell r="F57" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G57" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58" t="str">
+            <v>S12052-003A0X</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>Ins.Cp.Turn.Dimmer &amp; Light RH</v>
+          </cell>
+          <cell r="D58" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E58">
+            <v>665.0322580645161</v>
+          </cell>
+          <cell r="F58" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G58" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59" t="str">
+            <v>14SW311156-00002X0</v>
+          </cell>
+          <cell r="C59" t="str">
+            <v>INSULATOR</v>
+          </cell>
+          <cell r="D59" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E59">
+            <v>816.09677419354853</v>
+          </cell>
+          <cell r="F59" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G59" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>S03077-001A0X</v>
+          </cell>
+          <cell r="C60" t="str">
+            <v>COUPLER GUIDE 6P</v>
+          </cell>
+          <cell r="D60" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E60">
+            <v>94.161290322580641</v>
+          </cell>
+          <cell r="F60" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G60" t="str">
+            <v>Green</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>S03080-004A0X</v>
+          </cell>
+          <cell r="C61" t="str">
+            <v>COUPLER GUIDE</v>
+          </cell>
+          <cell r="D61" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E61">
+            <v>8.0322580645161281</v>
+          </cell>
+          <cell r="F61" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G61" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62" t="str">
+            <v>S250068-002</v>
+          </cell>
+          <cell r="C62" t="str">
+            <v>INSULATOR</v>
+          </cell>
+          <cell r="D62" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E62" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F62" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G62" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="B63" t="str">
+            <v>14SW311083-00005X0</v>
+          </cell>
+          <cell r="C63" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D63" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E63">
+            <v>460.64516129032262</v>
+          </cell>
+          <cell r="F63" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G63" t="str">
+            <v>Brown</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="B64" t="str">
+            <v>S11026-054A0X</v>
+          </cell>
+          <cell r="C64" t="str">
+            <v>Insulator Cp Dimmer &amp; Light RH</v>
+          </cell>
+          <cell r="D64" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E64">
+            <v>570.77419354838707</v>
+          </cell>
+          <cell r="F64" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G64" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="B65" t="str">
+            <v>14SW110487-00002X0</v>
+          </cell>
+          <cell r="C65" t="str">
+            <v>INSULATOR CP RR WIPER</v>
+          </cell>
+          <cell r="D65" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E65">
+            <v>190.25806451612902</v>
+          </cell>
+          <cell r="F65" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G65" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="B66" t="str">
+            <v>S01100-004A0X</v>
+          </cell>
+          <cell r="C66" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D66" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E66" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F66" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G66" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="B67" t="str">
+            <v>S250069-001</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>INSULATOR</v>
+          </cell>
+          <cell r="D67" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E67" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F67" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G67" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="B68" t="str">
+            <v>14SW311082-00010X0</v>
+          </cell>
+          <cell r="C68" t="str">
+            <v>INSULATOR</v>
+          </cell>
+          <cell r="D68" t="str">
+            <v>M.P-08</v>
+          </cell>
+          <cell r="E68">
+            <v>475.9354838709678</v>
+          </cell>
+          <cell r="F68" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G68" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="B69" t="str">
+            <v>S12042-004A9X</v>
+          </cell>
+          <cell r="C69" t="str">
+            <v>INSULATOR CP FOG RH</v>
+          </cell>
+          <cell r="D69" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E69">
+            <v>1200</v>
+          </cell>
+          <cell r="F69" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G69" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="B70" t="str">
+            <v>14SW311083-00005X0</v>
+          </cell>
+          <cell r="C70" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D70" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E70">
+            <v>460.64516129032262</v>
+          </cell>
+          <cell r="F70" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G70" t="str">
+            <v>Brown</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="B71" t="str">
+            <v>M41224-022A0X</v>
+          </cell>
+          <cell r="C71" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D71" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E71" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F71" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G71" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="B72" t="str">
+            <v>S33045-010A0X</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>TERMINAL COMP</v>
+          </cell>
+          <cell r="D72" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E72">
+            <v>1.161290322580645</v>
+          </cell>
+          <cell r="F72" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G72" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="B73" t="str">
+            <v>S31777-003A0X</v>
+          </cell>
+          <cell r="C73" t="str">
+            <v>BASE</v>
+          </cell>
+          <cell r="D73" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E73">
+            <v>720.58064516129025</v>
+          </cell>
+          <cell r="F73" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G73" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="B74" t="str">
+            <v>S12089-004A0X</v>
+          </cell>
+          <cell r="C74" t="str">
+            <v>INSULATOR CP, FOG, LH</v>
+          </cell>
+          <cell r="D74" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E74">
+            <v>1834.3548387096776</v>
+          </cell>
+          <cell r="F74" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G74" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="B75" t="str">
+            <v>S12102-001A0X</v>
+          </cell>
+          <cell r="C75" t="str">
+            <v>CONNECTOR CP FOG RH</v>
+          </cell>
+          <cell r="D75" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E75">
+            <v>222.29032258064515</v>
+          </cell>
+          <cell r="F75" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G75" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="B76" t="str">
+            <v>S32168-007A0X</v>
+          </cell>
+          <cell r="C76" t="str">
+            <v>PIN HEADER</v>
+          </cell>
+          <cell r="D76" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E76">
+            <v>1202.7096774193546</v>
+          </cell>
+          <cell r="F76" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G76" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="B77" t="str">
+            <v>S12089-001A0X</v>
+          </cell>
+          <cell r="C77" t="str">
+            <v>CONNECTOR CP FOG LH</v>
+          </cell>
+          <cell r="D77" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E77">
+            <v>332.41935483870969</v>
+          </cell>
+          <cell r="F77" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G77" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="B78" t="str">
+            <v>S11332-002A0X</v>
+          </cell>
+          <cell r="C78" t="str">
+            <v>BASE, FOG.(R)</v>
+          </cell>
+          <cell r="D78" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E78">
+            <v>0.67741935483870963</v>
+          </cell>
+          <cell r="F78" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G78" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="B79" t="str">
+            <v>14SW210274-00016X0</v>
+          </cell>
+          <cell r="C79" t="str">
+            <v>INSULATOR CP, AUTO</v>
+          </cell>
+          <cell r="D79" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E79">
+            <v>7373.2258064516118</v>
+          </cell>
+          <cell r="F79" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G79" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="B80" t="str">
+            <v>14SW210274-00013X0</v>
+          </cell>
+          <cell r="C80" t="str">
+            <v>CONTACT CP</v>
+          </cell>
+          <cell r="D80" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E80">
+            <v>7373.2258064516118</v>
+          </cell>
+          <cell r="F80" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G80" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="B81" t="str">
+            <v>14SW311156-00002X0</v>
+          </cell>
+          <cell r="C81" t="str">
+            <v>INSULATOR</v>
+          </cell>
+          <cell r="D81" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E81">
+            <v>816.09677419354853</v>
+          </cell>
+          <cell r="F81" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G81" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="B82" t="str">
+            <v>14SW311038-00005X0</v>
+          </cell>
+          <cell r="C82" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D82" t="str">
+            <v>M.P-09</v>
+          </cell>
+          <cell r="E82">
+            <v>1178.7096774193546</v>
+          </cell>
+          <cell r="F82" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G82" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="B83" t="str">
+            <v>S21175-002</v>
+          </cell>
+          <cell r="C83" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D83" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E83" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F83" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G83" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="B84" t="str">
+            <v>S12087-004</v>
+          </cell>
+          <cell r="C84" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D84" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E84" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F84" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G84" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="B85" t="str">
+            <v>S11398-030A0X</v>
+          </cell>
+          <cell r="C85" t="str">
+            <v>INSULATOR CP WIPER RH</v>
+          </cell>
+          <cell r="D85" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E85">
+            <v>420</v>
+          </cell>
+          <cell r="F85" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G85" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="B86" t="str">
+            <v>S11398-018A0X</v>
+          </cell>
+          <cell r="C86" t="str">
+            <v>INSULATOR CP LIGHT RH</v>
+          </cell>
+          <cell r="D86" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E86">
+            <v>129.96774193548387</v>
+          </cell>
+          <cell r="F86" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G86" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="B87" t="str">
+            <v>S22166-016A0X</v>
+          </cell>
+          <cell r="C87" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D87" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E87">
+            <v>248.0322580645161</v>
+          </cell>
+          <cell r="F87" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G87" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="B88" t="str">
+            <v>S13088-007A0X</v>
+          </cell>
+          <cell r="C88" t="str">
+            <v>INSULATOR CP,WIPER,RH</v>
+          </cell>
+          <cell r="D88" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E88">
+            <v>21.677419354838708</v>
+          </cell>
+          <cell r="F88" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G88" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="B89" t="str">
+            <v>S13116-011A0X</v>
+          </cell>
+          <cell r="C89" t="str">
+            <v>INSULATOR CP, WIPER, RH</v>
+          </cell>
+          <cell r="D89" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E89">
+            <v>443.90322580645159</v>
+          </cell>
+          <cell r="F89" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="B90" t="str">
+            <v>S13120-001A0X</v>
+          </cell>
+          <cell r="C90" t="str">
+            <v>INSULATOR CP, WIPER, RH</v>
+          </cell>
+          <cell r="D90" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E90">
+            <v>128.80645161290323</v>
+          </cell>
+          <cell r="F90" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G90" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="B91" t="str">
+            <v>S33107-005A0X</v>
+          </cell>
+          <cell r="C91" t="str">
+            <v>BASE AUDIO B</v>
+          </cell>
+          <cell r="D91" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E91">
+            <v>78.290322580645167</v>
+          </cell>
+          <cell r="F91" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G91" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="B92" t="str">
+            <v>S13098-005A0X</v>
+          </cell>
+          <cell r="C92" t="str">
+            <v>PIECE TURN &amp; WIPER</v>
+          </cell>
+          <cell r="D92" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E92">
+            <v>5.225806451612903</v>
+          </cell>
+          <cell r="F92" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G92" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="B93" t="str">
+            <v>S13094-014A0X</v>
+          </cell>
+          <cell r="C93" t="str">
+            <v>INSULATOR CP. WIPER RH</v>
+          </cell>
+          <cell r="D93" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E93">
+            <v>26.129032258064512</v>
+          </cell>
+          <cell r="F93" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G93" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="B94" t="str">
+            <v>S13081-004A0X</v>
+          </cell>
+          <cell r="C94" t="str">
+            <v>INSULATOR CP. WIPER LH</v>
+          </cell>
+          <cell r="D94" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E94">
+            <v>0.67741935483870963</v>
+          </cell>
+          <cell r="F94" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G94" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="B95" t="str">
+            <v>14SW030082-00001X0</v>
+          </cell>
+          <cell r="C95" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D95" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E95">
+            <v>479.70967741935488</v>
+          </cell>
+          <cell r="F95" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G95" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="B96" t="str">
+            <v>S13080-004A0X</v>
+          </cell>
+          <cell r="C96" t="str">
+            <v>INSULATOR CP. WIPER RH</v>
+          </cell>
+          <cell r="D96" t="str">
+            <v>M.P-10</v>
+          </cell>
+          <cell r="E96">
+            <v>74.516129032258064</v>
+          </cell>
+          <cell r="F96" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G96" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="B97" t="str">
+            <v>S12104-006A0X</v>
+          </cell>
+          <cell r="C97" t="str">
+            <v>INSULATOR CP TURN DIMMER &amp; LIGHT RH</v>
+          </cell>
+          <cell r="D97" t="str">
+            <v>M.P-11</v>
+          </cell>
+          <cell r="E97">
+            <v>4107.2903225806449</v>
+          </cell>
+          <cell r="F97" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G97">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="B98" t="str">
+            <v>S12095-004A0X</v>
+          </cell>
+          <cell r="C98" t="str">
+            <v>INSULATOR CP,TURN DIMMER &amp; LIGHT,LH</v>
+          </cell>
+          <cell r="D98" t="str">
+            <v>M.P-11</v>
+          </cell>
+          <cell r="E98">
+            <v>1420.258064516129</v>
+          </cell>
+          <cell r="F98" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G98" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="B99" t="str">
+            <v>S32197-006A0X</v>
+          </cell>
+          <cell r="C99" t="str">
+            <v>PIN HEADER</v>
+          </cell>
+          <cell r="D99" t="str">
+            <v>M.P-12</v>
+          </cell>
+          <cell r="E99">
+            <v>15606.58064516129</v>
+          </cell>
+          <cell r="F99" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G99" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="B100" t="str">
+            <v>S12042-004A9X</v>
+          </cell>
+          <cell r="C100" t="str">
+            <v>INSULATOR CP FOG RH</v>
+          </cell>
+          <cell r="D100" t="str">
+            <v>M.P-12</v>
+          </cell>
+          <cell r="E100">
+            <v>1200</v>
+          </cell>
+          <cell r="F100" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G100" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="B101" t="str">
+            <v>S32168-007A0X</v>
+          </cell>
+          <cell r="C101" t="str">
+            <v>PIN HEADER</v>
+          </cell>
+          <cell r="D101" t="str">
+            <v>M.P-12</v>
+          </cell>
+          <cell r="E101">
+            <v>1202.7096774193546</v>
+          </cell>
+          <cell r="F101" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G101" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="B102" t="str">
+            <v>S11436-002</v>
+          </cell>
+          <cell r="C102" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D102" t="str">
+            <v>M.P-12</v>
+          </cell>
+          <cell r="E102" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F102" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G102" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="B103" t="str">
+            <v>S31437-004A0X</v>
+          </cell>
+          <cell r="C103" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D103" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E103">
+            <v>6278.6129032258068</v>
+          </cell>
+          <cell r="F103" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G103" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="B104" t="str">
+            <v>S07023-002A0X</v>
+          </cell>
+          <cell r="C104" t="str">
+            <v>INSULATOR</v>
+          </cell>
+          <cell r="D104" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E104">
+            <v>361.54838709677421</v>
+          </cell>
+          <cell r="F104" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G104" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="B105" t="str">
+            <v>S13123-002A0X</v>
+          </cell>
+          <cell r="C105" t="str">
+            <v>INSULATOR CP RR WIPER LH</v>
+          </cell>
+          <cell r="D105" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E105">
+            <v>499.45161290322574</v>
+          </cell>
+          <cell r="F105" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G105" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="B106" t="str">
+            <v>S31740-008A0X</v>
+          </cell>
+          <cell r="C106" t="str">
+            <v>PIN HEADER CP</v>
+          </cell>
+          <cell r="D106" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E106">
+            <v>162.09677419354838</v>
+          </cell>
+          <cell r="F106" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G106" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="B107" t="str">
+            <v>S12091-001A0X</v>
+          </cell>
+          <cell r="C107" t="str">
+            <v>INSULATOR CP, FOG, LH</v>
+          </cell>
+          <cell r="D107" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E107">
+            <v>277.25806451612902</v>
+          </cell>
+          <cell r="F107" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G107" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="B108" t="str">
+            <v>S13052-005A0X</v>
+          </cell>
+          <cell r="C108" t="str">
+            <v>CONTACT CP.RR.WI</v>
+          </cell>
+          <cell r="D108" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E108">
+            <v>488.80645161290323</v>
+          </cell>
+          <cell r="F108" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G108" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="B109" t="str">
+            <v>S12094-001A0X</v>
+          </cell>
+          <cell r="C109" t="str">
+            <v>CONNECTOR CP. AUTO LIGHT RH</v>
+          </cell>
+          <cell r="D109" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E109">
+            <v>5.225806451612903</v>
+          </cell>
+          <cell r="F109" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G109" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="B110" t="str">
+            <v>S11038-029A0X</v>
+          </cell>
+          <cell r="C110" t="str">
+            <v>Base Insert LT</v>
+          </cell>
+          <cell r="D110" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E110">
+            <v>53.516129032258064</v>
+          </cell>
+          <cell r="F110" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G110" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="B111" t="str">
+            <v>S31135-011A0X</v>
+          </cell>
+          <cell r="C111" t="str">
+            <v>Base Cp</v>
+          </cell>
+          <cell r="D111" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E111">
+            <v>58.064516129032256</v>
+          </cell>
+          <cell r="F111" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G111" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="B112" t="str">
+            <v>S03044-005A0X</v>
+          </cell>
+          <cell r="C112" t="str">
+            <v>Insulator B</v>
+          </cell>
+          <cell r="D112" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E112">
+            <v>10.451612903225806</v>
+          </cell>
+          <cell r="F112" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G112" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="B113" t="str">
+            <v>S11340-008A0X</v>
+          </cell>
+          <cell r="C113" t="str">
+            <v>PIECE CP RW. (R)</v>
+          </cell>
+          <cell r="D113" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E113">
+            <v>0</v>
+          </cell>
+          <cell r="F113" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G113" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="B114" t="str">
+            <v>S11122-015A0X</v>
+          </cell>
+          <cell r="C114" t="str">
+            <v>Base RW</v>
+          </cell>
+          <cell r="D114" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E114">
+            <v>0</v>
+          </cell>
+          <cell r="F114" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G114" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="B115" t="str">
+            <v>S13092-004A0X</v>
+          </cell>
+          <cell r="C115" t="str">
+            <v>CONNECTOR CP. AUTO, RH</v>
+          </cell>
+          <cell r="D115" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E115">
+            <v>0</v>
+          </cell>
+          <cell r="F115" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G115" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="B116" t="str">
+            <v>S12095-011A0X</v>
+          </cell>
+          <cell r="C116" t="str">
+            <v>CONTACT CP, LIGHT</v>
+          </cell>
+          <cell r="D116" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E116">
+            <v>2131.8387096774195</v>
+          </cell>
+          <cell r="F116" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G116" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="B117" t="str">
+            <v>S310966-002</v>
+          </cell>
+          <cell r="C117" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D117" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E117" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F117" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G117" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="B118" t="str">
+            <v>14SW220197-00010X0</v>
+          </cell>
+          <cell r="C118" t="str">
+            <v>PIN HEADER</v>
+          </cell>
+          <cell r="D118" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E118">
+            <v>2359.8387096774195</v>
+          </cell>
+          <cell r="F118" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G118" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="B119" t="str">
+            <v>S12095-003A0X</v>
+          </cell>
+          <cell r="C119" t="str">
+            <v>CONTACT CP, DIMMER, LH</v>
+          </cell>
+          <cell r="D119" t="str">
+            <v>M.P-13</v>
+          </cell>
+          <cell r="E119">
+            <v>2537.2258064516127</v>
+          </cell>
+          <cell r="F119" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G119" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="B120" t="str">
+            <v>S02020-010A0X</v>
+          </cell>
+          <cell r="C120" t="str">
+            <v>Stator Sub-CP</v>
+          </cell>
+          <cell r="D120" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E120">
+            <v>290.51612903225805</v>
+          </cell>
+          <cell r="F120" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G120" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="B121" t="str">
+            <v>S21021-021A0X</v>
+          </cell>
+          <cell r="C121" t="str">
+            <v>Connector Cp.</v>
+          </cell>
+          <cell r="D121" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E121" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F121" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G121" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="B122" t="str">
+            <v>S21007-038A0X</v>
+          </cell>
+          <cell r="C122" t="str">
+            <v>SWITCH BODY CP</v>
+          </cell>
+          <cell r="D122" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E122" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F122" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G122" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="B123" t="str">
+            <v>S13114-003A0X</v>
+          </cell>
+          <cell r="C123" t="str">
+            <v>INSULATOR CP.RR WIPER RH</v>
+          </cell>
+          <cell r="D123" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E123">
+            <v>20.903225806451612</v>
+          </cell>
+          <cell r="F123" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G123" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="B124" t="str">
+            <v>S13071-012A0X</v>
+          </cell>
+          <cell r="C124" t="str">
+            <v>Contact CP RR Wiper</v>
+          </cell>
+          <cell r="D124" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E124">
+            <v>5.903225806451613</v>
+          </cell>
+          <cell r="F124" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G124" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="B125" t="str">
+            <v>S11358-028A0X</v>
+          </cell>
+          <cell r="C125" t="str">
+            <v>CONNECTOR CP MAIN</v>
+          </cell>
+          <cell r="D125" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E125">
+            <v>0</v>
+          </cell>
+          <cell r="F125" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G125" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="B126" t="str">
+            <v>S21009-009A0X</v>
+          </cell>
+          <cell r="C126" t="str">
+            <v>SW BODY W CP.</v>
+          </cell>
+          <cell r="D126" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E126" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F126" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G126" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="B127" t="str">
+            <v>14SW210274-00016X0</v>
+          </cell>
+          <cell r="C127" t="str">
+            <v>INSULATOR CP, AUTO</v>
+          </cell>
+          <cell r="D127" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E127">
+            <v>7373.2258064516118</v>
+          </cell>
+          <cell r="F127" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G127" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="B128" t="str">
+            <v>14SW220201-00010X0</v>
+          </cell>
+          <cell r="C128" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D128" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E128">
+            <v>10746.870967741936</v>
+          </cell>
+          <cell r="F128" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G128" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="B129" t="str">
+            <v>S03066-001A0X</v>
+          </cell>
+          <cell r="C129" t="str">
+            <v>CASE</v>
+          </cell>
+          <cell r="D129" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E129">
+            <v>199.45161290322579</v>
+          </cell>
+          <cell r="F129" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G129" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="B130" t="str">
+            <v>S13083-011A0X</v>
+          </cell>
+          <cell r="C130" t="str">
+            <v>INSULATOR CP,RR WIPER,LH</v>
+          </cell>
+          <cell r="D130" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E130">
+            <v>1594.0645161290322</v>
+          </cell>
+          <cell r="F130" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G130" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="B131" t="str">
+            <v>14SW210274-00013X0</v>
+          </cell>
+          <cell r="C131" t="str">
+            <v>CONTACT CP</v>
+          </cell>
+          <cell r="D131" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E131">
+            <v>7373.2258064516118</v>
+          </cell>
+          <cell r="F131" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G131" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="B132" t="str">
+            <v>S311010-03</v>
+          </cell>
+          <cell r="C132" t="str">
+            <v>Contact CP</v>
+          </cell>
+          <cell r="D132" t="str">
+            <v>M.P-14</v>
+          </cell>
+          <cell r="E132" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F132" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G132" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="B133" t="str">
+            <v>S13108-002A0X</v>
+          </cell>
+          <cell r="C133" t="str">
+            <v>INSULATOR. CP WIPER RH</v>
+          </cell>
+          <cell r="D133" t="str">
+            <v>M.P-15</v>
+          </cell>
+          <cell r="E133">
+            <v>15621.096774193549</v>
+          </cell>
+          <cell r="F133" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G133" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="B134" t="str">
+            <v>S13083-003A0X</v>
+          </cell>
+          <cell r="C134" t="str">
+            <v>INSULATOR CP WIPER LH</v>
+          </cell>
+          <cell r="D134" t="str">
+            <v>M.P-15</v>
+          </cell>
+          <cell r="E134">
+            <v>2579.6129032258063</v>
+          </cell>
+          <cell r="F134" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G134" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="B135" t="str">
+            <v>S31121-012A0X</v>
+          </cell>
+          <cell r="C135" t="str">
+            <v>BASE CP.</v>
+          </cell>
+          <cell r="D135" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E135">
+            <v>8395.5483870967746</v>
+          </cell>
+          <cell r="F135" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G135" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="B136" t="str">
+            <v>S31064-006A0X</v>
+          </cell>
+          <cell r="C136" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D136" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E136">
+            <v>40.258064516129032</v>
+          </cell>
+          <cell r="F136" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G136" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="B137" t="str">
+            <v>S31123-005A0X</v>
+          </cell>
+          <cell r="C137" t="str">
+            <v>Base Cp.</v>
+          </cell>
+          <cell r="D137" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E137">
+            <v>168.09677419354838</v>
+          </cell>
+          <cell r="F137" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G137" t="str">
+            <v>Green</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="B138" t="str">
+            <v>S03080-004A0X</v>
+          </cell>
+          <cell r="C138" t="str">
+            <v>COUPLER GUIDE</v>
+          </cell>
+          <cell r="D138" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E138">
+            <v>8.0322580645161281</v>
+          </cell>
+          <cell r="F138" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G138" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="B139" t="str">
+            <v>S12106-001A0X</v>
+          </cell>
+          <cell r="C139" t="str">
+            <v>CONNECTOR CP AUTO LIGHT AND FOG RH</v>
+          </cell>
+          <cell r="D139" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E139">
+            <v>10.451612903225806</v>
+          </cell>
+          <cell r="F139" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G139" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="B140" t="str">
+            <v>S11160-006A0X</v>
+          </cell>
+          <cell r="C140" t="str">
+            <v>Base FR &amp; RR Fog R</v>
+          </cell>
+          <cell r="D140" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E140">
+            <v>2.129032258064516</v>
+          </cell>
+          <cell r="F140" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G140" t="str">
+            <v>Blue</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="B141" t="str">
+            <v>S31851-002A0X</v>
+          </cell>
+          <cell r="C141" t="str">
+            <v>BASE CP</v>
+          </cell>
+          <cell r="D141" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E141">
+            <v>0.38709677419354838</v>
+          </cell>
+          <cell r="F141" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G141" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="B142" t="str">
+            <v>S31068-005A0X</v>
+          </cell>
+          <cell r="C142" t="str">
+            <v>Base CP</v>
+          </cell>
+          <cell r="D142" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E142">
+            <v>1.3548387096774193</v>
+          </cell>
+          <cell r="F142" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G142" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="B143" t="str">
+            <v>S31605-002A0X</v>
+          </cell>
+          <cell r="C143" t="str">
+            <v>BASE CP.</v>
+          </cell>
+          <cell r="D143" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E143">
+            <v>0.38709677419354838</v>
+          </cell>
+          <cell r="F143" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G143" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="B144" t="str">
+            <v>S33045-009A0X</v>
+          </cell>
+          <cell r="C144" t="str">
+            <v>BASE AUDIO</v>
+          </cell>
+          <cell r="D144" t="str">
+            <v>M.P-16</v>
+          </cell>
+          <cell r="E144">
+            <v>0.38709677419354838</v>
+          </cell>
+          <cell r="F144" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G144" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="B145" t="str">
+            <v>14SW220201-00005X0</v>
+          </cell>
+          <cell r="C145" t="str">
+            <v>CONNECTOR CP</v>
+          </cell>
+          <cell r="D145" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E145">
+            <v>792.09677419354853</v>
+          </cell>
+          <cell r="F145" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G145" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="B146" t="str">
+            <v>S21021-016A0X</v>
+          </cell>
+          <cell r="C146" t="str">
+            <v>Connector Cp.</v>
+          </cell>
+          <cell r="D146" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E146">
+            <v>528.58064516129025</v>
+          </cell>
+          <cell r="F146" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G146" t="str">
+            <v>Brown</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="B147" t="str">
+            <v>S41354-011A0X</v>
+          </cell>
+          <cell r="C147" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D147" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E147">
+            <v>1768.8387096774195</v>
+          </cell>
+          <cell r="F147" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G147" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="B148" t="str">
+            <v>S21021-012A0X</v>
+          </cell>
+          <cell r="C148" t="str">
+            <v>Insulator Cp</v>
+          </cell>
+          <cell r="D148" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E148">
+            <v>604.0645161290322</v>
+          </cell>
+          <cell r="F148" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G148" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="B149" t="str">
+            <v>S11434-002A0X</v>
+          </cell>
+          <cell r="C149" t="str">
+            <v>INSULATOR CP LIGHT RH</v>
+          </cell>
+          <cell r="D149" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E149">
+            <v>563.51612903225805</v>
+          </cell>
+          <cell r="F149" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G149" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="B150" t="str">
+            <v>S21077-008A0X</v>
+          </cell>
+          <cell r="C150" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D150" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E150" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F150" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G150" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="B151" t="str">
+            <v>S120197-005</v>
+          </cell>
+          <cell r="C151" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D151" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E151" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F151" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G151" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="B152" t="str">
+            <v>14SW110487-00009X0</v>
+          </cell>
+          <cell r="C152" t="str">
+            <v>INSULATOR CP. WIPER RH</v>
+          </cell>
+          <cell r="D152" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E152">
+            <v>190.25806451612902</v>
+          </cell>
+          <cell r="F152" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G152" t="str">
+            <v>Blue</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="B153" t="str">
+            <v>S110432-007</v>
+          </cell>
+          <cell r="C153" t="str">
+            <v>INSULATOR CP</v>
+          </cell>
+          <cell r="D153" t="str">
+            <v>M.P-17</v>
+          </cell>
+          <cell r="E153" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F153" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G153" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="B154" t="str">
+            <v>S21174-014A0X</v>
+          </cell>
+          <cell r="D154" t="str">
+            <v>TOYO 1ST</v>
+          </cell>
+          <cell r="E154">
+            <v>1900.6451612903224</v>
+          </cell>
+          <cell r="F154" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G154" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="B155" t="str">
+            <v>S41356-017A0X</v>
+          </cell>
+          <cell r="D155" t="str">
+            <v>TOYO 1ST</v>
+          </cell>
+          <cell r="E155">
+            <v>368.32258064516134</v>
+          </cell>
+          <cell r="F155" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G155" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="B156" t="str">
+            <v>14SW210274-00008X0</v>
+          </cell>
+          <cell r="D156" t="str">
+            <v>TOYO 1ST</v>
+          </cell>
+          <cell r="E156">
+            <v>22119.677419354837</v>
+          </cell>
+          <cell r="F156" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G156" t="str">
+            <v>Blue</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="B157" t="str">
+            <v>S25038-001A0X</v>
+          </cell>
+          <cell r="D157" t="str">
+            <v>TOYO 2ND</v>
+          </cell>
+          <cell r="E157">
+            <v>7344.7741935483882</v>
+          </cell>
+          <cell r="F157" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G157" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="B158" t="str">
+            <v>S25026-003A0X</v>
+          </cell>
+          <cell r="D158" t="str">
+            <v>TOYO 2ND</v>
+          </cell>
+          <cell r="E158">
+            <v>79.838709677419359</v>
+          </cell>
+          <cell r="F158" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G158" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="B159" t="str">
+            <v>S21174-012A0X</v>
+          </cell>
+          <cell r="D159" t="str">
+            <v>TOYO 3RD</v>
+          </cell>
+          <cell r="E159">
+            <v>28041.774193548386</v>
+          </cell>
+          <cell r="F159" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G159" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="B160" t="str">
+            <v>S21174-012A0X</v>
+          </cell>
+          <cell r="D160" t="str">
+            <v>TOYO 4TH</v>
+          </cell>
+          <cell r="E160">
+            <v>28041.774193548386</v>
+          </cell>
+          <cell r="F160" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G160" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="B161" t="str">
+            <v>14SW220201-00010X0</v>
+          </cell>
+          <cell r="D161" t="str">
+            <v>TOYO 5TH</v>
+          </cell>
+          <cell r="E161">
+            <v>10746.870967741936</v>
+          </cell>
+          <cell r="F161" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G161" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="B162" t="str">
+            <v>14SW250069-00001X0</v>
+          </cell>
+          <cell r="D162" t="str">
+            <v>TOYO 6TH</v>
+          </cell>
+          <cell r="E162">
+            <v>1295.3225806451612</v>
+          </cell>
+          <cell r="F162" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G162" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="B163" t="str">
+            <v>14SW250068-00003X0</v>
+          </cell>
+          <cell r="D163" t="str">
+            <v>TOYO 6TH</v>
+          </cell>
+          <cell r="E163">
+            <v>2507.4193548387093</v>
+          </cell>
+          <cell r="F163" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G163" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="B164" t="str">
+            <v>14SW250069-00002X1</v>
+          </cell>
+          <cell r="D164" t="str">
+            <v>TOYO 6TH</v>
+          </cell>
+          <cell r="E164" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F164" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G164" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="B165" t="str">
+            <v>14SW220207-00003X0</v>
+          </cell>
+          <cell r="D165" t="str">
+            <v>TOYO 6TH</v>
+          </cell>
+          <cell r="E165">
+            <v>5857.1612903225814</v>
+          </cell>
+          <cell r="F165" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G165" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="B166" t="str">
+            <v>S03046-005A0X</v>
+          </cell>
+          <cell r="D166" t="str">
+            <v>TOYO 7TH</v>
+          </cell>
+          <cell r="E166">
+            <v>2249.2258064516127</v>
+          </cell>
+          <cell r="F166" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G166" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="B167" t="str">
+            <v>S01100-004A9X</v>
+          </cell>
+          <cell r="D167" t="str">
+            <v>TOYO 7TH</v>
+          </cell>
+          <cell r="E167">
+            <v>4869.1935483870966</v>
+          </cell>
+          <cell r="F167" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G167" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="B168" t="str">
+            <v>S12052-003A0X</v>
+          </cell>
+          <cell r="D168" t="str">
+            <v>TOYO 7TH</v>
+          </cell>
+          <cell r="E168">
+            <v>665.0322580645161</v>
+          </cell>
+          <cell r="F168" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G168" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="B169" t="str">
+            <v>S13110-005A0X</v>
+          </cell>
+          <cell r="D169" t="str">
+            <v>TOYO 7TH</v>
+          </cell>
+          <cell r="E169">
+            <v>1706.516129032258</v>
+          </cell>
+          <cell r="F169" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G169" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="B170" t="str">
+            <v>S12087-004A0X</v>
+          </cell>
+          <cell r="D170" t="str">
+            <v>TOYO 80T 2ND</v>
+          </cell>
+          <cell r="E170">
+            <v>1017.1935483870968</v>
+          </cell>
+          <cell r="F170" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G170" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="B171" t="str">
+            <v>S12100-003A0X</v>
+          </cell>
+          <cell r="D171" t="str">
+            <v>TOYO 80T 1ST</v>
+          </cell>
+          <cell r="E171">
+            <v>8150.3225806451619</v>
+          </cell>
+          <cell r="F171" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G171" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="B172" t="str">
+            <v>S33105-016A0X</v>
+          </cell>
+          <cell r="D172" t="str">
+            <v>TOYO 80T 2ND</v>
+          </cell>
+          <cell r="E172">
+            <v>1226.4193548387098</v>
+          </cell>
+          <cell r="F172" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G172" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="B173" t="str">
+            <v>14SW330127-00008X0</v>
+          </cell>
+          <cell r="D173" t="str">
+            <v>TOYO 80T 2ND</v>
+          </cell>
+          <cell r="E173">
+            <v>782.41935483870975</v>
+          </cell>
+          <cell r="F173" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G173" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="B174" t="str">
+            <v>S33106-009A0X</v>
+          </cell>
+          <cell r="D174" t="str">
+            <v>TOYO 80T 1ST</v>
+          </cell>
+          <cell r="E174">
+            <v>63.87096774193548</v>
+          </cell>
+          <cell r="F174" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G174" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="B175" t="str">
+            <v>S13108-002A0X</v>
+          </cell>
+          <cell r="D175" t="str">
+            <v>TOYO 80T 2ND</v>
+          </cell>
+          <cell r="E175">
+            <v>15621.096774193549</v>
+          </cell>
+          <cell r="F175" t="str">
+            <v>INJ.MOULD. M/C(</v>
+          </cell>
+          <cell r="G175" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="B176" t="str">
+            <v>S22127-003A0X</v>
+          </cell>
+          <cell r="D176" t="str">
+            <v>JSW 1ST</v>
+          </cell>
+          <cell r="E176">
+            <v>15855.774193548386</v>
+          </cell>
+          <cell r="F176" t="str">
+            <v>INJ.MOULD. M/C V</v>
+          </cell>
+          <cell r="G176" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="B177" t="str">
+            <v>S03058-002A0X</v>
+          </cell>
+          <cell r="D177" t="str">
+            <v>YUDEK 1ST</v>
+          </cell>
+          <cell r="E177">
+            <v>14191.645161290324</v>
+          </cell>
+          <cell r="F177" t="str">
+            <v>INJ.MOULD. M/C (YUDEK)V</v>
+          </cell>
+          <cell r="G177" t="str">
+            <v>White</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="B178" t="str">
+            <v>S03062-001A0X</v>
+          </cell>
+          <cell r="D178" t="str">
+            <v>YUDEK 1ST</v>
+          </cell>
+          <cell r="E178" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="F178" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G178" t="e">
+            <v>#N/A</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6720,23 +9533,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB791F3A-917C-4E15-B913-91965FB6F290}">
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" style="2" customWidth="1"/>
-    <col min="3" max="7" width="23.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="44.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="33.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" style="2" customWidth="1"/>
+    <col min="3" max="8" width="23.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="30.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="44.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="33.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -6746,44 +9559,47 @@
       <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>46024</v>
       </c>
@@ -6793,47 +9609,51 @@
       <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="6" t="str">
+        <f>VLOOKUP(C2, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E2" s="6">
         <f>VLOOKUP(C2, [1]VT!C:G, 5, FALSE)</f>
         <v>15</v>
       </c>
-      <c r="E2" s="6">
+      <c r="F2" s="6">
         <f>VLOOKUP(C2, [1]VT!C:H, 6, FALSE)</f>
         <v>90</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="6">
         <f>VLOOKUP(C2, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="2">
         <v>90</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>6</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>768</v>
       </c>
-      <c r="M2" s="2">
+      <c r="N2" s="2">
         <v>669</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>21</v>
       </c>
-      <c r="O2" s="2">
+      <c r="P2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46024</v>
       </c>
@@ -6843,47 +9663,51 @@
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="6" t="str">
+        <f>VLOOKUP(C3, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E3" s="6">
         <f>VLOOKUP(C3, [1]VT!C:G, 5, FALSE)</f>
         <v>16</v>
       </c>
-      <c r="E3" s="6">
+      <c r="F3" s="6">
         <f>VLOOKUP(C3, [1]VT!C:H, 6, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="6">
         <f>VLOOKUP(C3, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="2">
         <v>80</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="2">
         <v>4</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
         <v>320</v>
       </c>
-      <c r="M3" s="2">
+      <c r="N3" s="2">
         <v>257</v>
       </c>
-      <c r="N3" s="2">
+      <c r="O3" s="2">
         <v>23</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>46024</v>
       </c>
@@ -6893,47 +9717,51 @@
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="6" t="str">
+        <f>VLOOKUP(C4, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E4" s="6">
         <f>VLOOKUP(C4, [1]VT!C:G, 5, FALSE)</f>
         <v>16</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <f>VLOOKUP(C4, [1]VT!C:H, 6, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <f>VLOOKUP(C4, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="2">
         <v>80</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <v>4</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>320</v>
       </c>
-      <c r="M4" s="2">
+      <c r="N4" s="2">
         <v>280</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="2">
         <v>6</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46024</v>
       </c>
@@ -6943,47 +9771,51 @@
       <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="6" t="str">
+        <f>VLOOKUP(C5, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E5" s="6">
         <f>VLOOKUP(C5, [1]VT!C:G, 5, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <f>VLOOKUP(C5, [1]VT!C:H, 6, FALSE)</f>
         <v>384</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <f>VLOOKUP(C5, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>80</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <v>3</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>576</v>
       </c>
-      <c r="M5" s="2">
+      <c r="N5" s="2">
         <v>382</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <v>30</v>
       </c>
-      <c r="O5" s="2">
+      <c r="P5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>46024</v>
       </c>
@@ -6993,47 +9825,51 @@
       <c r="C6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="6" t="str">
+        <f>VLOOKUP(C6, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E6" s="6">
         <f>VLOOKUP(C6, [1]VT!C:G, 5, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <f>VLOOKUP(C6, [1]VT!C:H, 6, FALSE)</f>
         <v>200</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <f>VLOOKUP(C6, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="2">
         <v>140</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="2">
         <v>7</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>1400</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <v>1578</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2">
         <v>10</v>
       </c>
-      <c r="O6" s="2">
+      <c r="P6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>46024</v>
       </c>
@@ -7043,47 +9879,51 @@
       <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="6" t="str">
+        <f>VLOOKUP(C7, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E7" s="6">
         <f>VLOOKUP(C7, [1]VT!C:G, 5, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <f>VLOOKUP(C7, [1]VT!C:H, 6, FALSE)</f>
         <v>200</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <f>VLOOKUP(C7, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="2">
         <v>140</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>3</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>600</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>476</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>14</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>46024</v>
       </c>
@@ -7093,47 +9933,51 @@
       <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="6" t="str">
+        <f>VLOOKUP(C8, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E8" s="6">
         <f>VLOOKUP(C8, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <f>VLOOKUP(C8, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <f>VLOOKUP(C8, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="2">
         <v>80</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <v>4</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>560</v>
       </c>
-      <c r="M8" s="2">
+      <c r="N8" s="2">
         <v>508</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>22</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>46024</v>
       </c>
@@ -7143,47 +9987,51 @@
       <c r="C9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="6" t="str">
+        <f>VLOOKUP(C9, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E9" s="6">
         <f>VLOOKUP(C9, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <f>VLOOKUP(C9, [1]VT!C:H, 6, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <f>VLOOKUP(C9, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <v>55</v>
       </c>
-      <c r="K9" s="2">
+      <c r="L9" s="2">
         <v>5</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
         <v>400</v>
       </c>
-      <c r="M9" s="2">
+      <c r="N9" s="2">
         <v>416</v>
       </c>
-      <c r="N9" s="2">
+      <c r="O9" s="2">
         <v>25</v>
       </c>
-      <c r="O9" s="2">
+      <c r="P9" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>46024</v>
       </c>
@@ -7193,47 +10041,51 @@
       <c r="C10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="6" t="e">
+        <f>VLOOKUP(C10, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" s="6">
         <f>VLOOKUP(C10, [1]VT!C:G, 5, FALSE)</f>
         <v>104</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <f>VLOOKUP(C10, [1]VT!C:H, 6, FALSE)</f>
         <v>520</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <f>VLOOKUP(C10, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="2">
         <v>90</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <v>1</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>520</v>
       </c>
-      <c r="M10" s="2">
+      <c r="N10" s="2">
         <v>540</v>
       </c>
-      <c r="N10" s="2">
+      <c r="O10" s="2">
         <v>15</v>
       </c>
-      <c r="O10" s="2">
+      <c r="P10" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>46024</v>
       </c>
@@ -7243,47 +10095,51 @@
       <c r="C11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="6" t="e">
+        <f>VLOOKUP(C11, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="6">
         <f>VLOOKUP(C11, [1]VT!C:G, 5, FALSE)</f>
         <v>104</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="6">
         <f>VLOOKUP(C11, [1]VT!C:H, 6, FALSE)</f>
         <v>520</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="6">
         <f>VLOOKUP(C11, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="2">
         <v>70</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <v>2</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>1040</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <v>957</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <v>47</v>
       </c>
-      <c r="O11" s="2">
+      <c r="P11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>46024</v>
       </c>
@@ -7293,47 +10149,51 @@
       <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="6" t="str">
+        <f>VLOOKUP(C12, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E12" s="6">
         <f>VLOOKUP(C12, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="6">
         <f>VLOOKUP(C12, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="6">
         <f>VLOOKUP(C12, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <v>80</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <v>2</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>320</v>
       </c>
-      <c r="M12" s="2">
+      <c r="N12" s="2">
         <v>314</v>
       </c>
-      <c r="N12" s="2">
+      <c r="O12" s="2">
         <v>20</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>46024</v>
       </c>
@@ -7343,47 +10203,51 @@
       <c r="C13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="6" t="str">
+        <f>VLOOKUP(C13, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Brown</v>
+      </c>
+      <c r="E13" s="6">
         <f>VLOOKUP(C13, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E13" s="6">
+      <c r="F13" s="6">
         <f>VLOOKUP(C13, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="6">
         <f>VLOOKUP(C13, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="2">
         <v>140</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>3</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
         <v>576</v>
       </c>
-      <c r="M13" s="2">
+      <c r="N13" s="2">
         <v>649</v>
       </c>
-      <c r="N13" s="2">
+      <c r="O13" s="2">
         <v>7</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>46024</v>
       </c>
@@ -7393,47 +10257,51 @@
       <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="6" t="str">
+        <f>VLOOKUP(C14, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Brown</v>
+      </c>
+      <c r="E14" s="6">
         <f>VLOOKUP(C14, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="6">
         <f>VLOOKUP(C14, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <f>VLOOKUP(C14, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="2">
         <v>140</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <v>3</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <v>576</v>
       </c>
-      <c r="M14" s="2">
+      <c r="N14" s="2">
         <v>690</v>
       </c>
-      <c r="N14" s="2">
+      <c r="O14" s="2">
         <v>10</v>
       </c>
-      <c r="O14" s="2">
+      <c r="P14" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>46024</v>
       </c>
@@ -7443,47 +10311,51 @@
       <c r="C15" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="6" t="e">
+        <f>VLOOKUP(C15, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="6">
         <f>VLOOKUP(C15, [1]VT!C:G, 5, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="6">
         <f>VLOOKUP(C15, [1]VT!C:H, 6, FALSE)</f>
         <v>160</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <f>VLOOKUP(C15, [1]VT!C:I, 7, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <v>90</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="2">
         <v>3</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
         <v>480</v>
       </c>
-      <c r="M15" s="2">
+      <c r="N15" s="2">
         <v>348</v>
       </c>
-      <c r="N15" s="2">
+      <c r="O15" s="2">
         <v>18</v>
       </c>
-      <c r="O15" s="2">
+      <c r="P15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>46025</v>
       </c>
@@ -7493,47 +10365,51 @@
       <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="6" t="str">
+        <f>VLOOKUP(C16, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E16" s="6">
         <f>VLOOKUP(C16, [1]VT!C:G, 5, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="6">
         <f>VLOOKUP(C16, [1]VT!C:H, 6, FALSE)</f>
         <v>384</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="6">
         <f>VLOOKUP(C16, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="2">
         <v>80</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="2">
         <v>3</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
         <v>576</v>
       </c>
-      <c r="M16" s="2">
+      <c r="N16" s="2">
         <v>654</v>
       </c>
-      <c r="N16" s="2">
+      <c r="O16" s="2">
         <v>34</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>46025</v>
       </c>
@@ -7543,47 +10419,51 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="6" t="str">
+        <f>VLOOKUP(C17, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E17" s="6">
         <f>VLOOKUP(C17, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="6">
         <f>VLOOKUP(C17, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <f>VLOOKUP(C17, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="2">
         <v>100</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <v>25</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <v>1000</v>
       </c>
-      <c r="M17" s="2">
+      <c r="N17" s="2">
         <v>942</v>
       </c>
-      <c r="N17" s="2">
+      <c r="O17" s="2">
         <v>36</v>
       </c>
-      <c r="O17" s="2">
+      <c r="P17" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>46025</v>
       </c>
@@ -7593,47 +10473,51 @@
       <c r="C18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="6" t="str">
+        <f>VLOOKUP(C18, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E18" s="6">
         <f>VLOOKUP(C18, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E18" s="6">
+      <c r="F18" s="6">
         <f>VLOOKUP(C18, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="6">
         <f>VLOOKUP(C18, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="2">
         <v>80</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <v>5</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>400</v>
       </c>
-      <c r="M18" s="2">
+      <c r="N18" s="2">
         <v>287</v>
       </c>
-      <c r="N18" s="2">
+      <c r="O18" s="2">
         <v>29</v>
       </c>
-      <c r="O18" s="2">
+      <c r="P18" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>46025</v>
       </c>
@@ -7643,47 +10527,51 @@
       <c r="C19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="6" t="str">
+        <f>VLOOKUP(C19, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E19" s="6">
         <f>VLOOKUP(C19, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E19" s="6">
+      <c r="F19" s="6">
         <f>VLOOKUP(C19, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="6">
         <f>VLOOKUP(C19, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="2">
         <v>80</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <v>10</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
         <v>800</v>
       </c>
-      <c r="M19" s="2">
+      <c r="N19" s="2">
         <v>682</v>
       </c>
-      <c r="N19" s="2">
+      <c r="O19" s="2">
         <v>28</v>
       </c>
-      <c r="O19" s="2">
+      <c r="P19" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>46025</v>
       </c>
@@ -7693,47 +10581,51 @@
       <c r="C20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="6" t="str">
+        <f>VLOOKUP(C20, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E20" s="6">
         <f>VLOOKUP(C20, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E20" s="6">
+      <c r="F20" s="6">
         <f>VLOOKUP(C20, [1]VT!C:H, 6, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="6">
         <f>VLOOKUP(C20, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="2">
         <v>30</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <v>21</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <v>160</v>
       </c>
-      <c r="M20" s="2">
+      <c r="N20" s="2">
         <v>301</v>
       </c>
-      <c r="N20" s="2">
+      <c r="O20" s="2">
         <v>24</v>
       </c>
-      <c r="O20" s="2">
+      <c r="P20" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>46025</v>
       </c>
@@ -7743,47 +10635,51 @@
       <c r="C21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="6" t="str">
+        <f>VLOOKUP(C21, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E21" s="6">
         <f>VLOOKUP(C21, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F21" s="6">
         <f>VLOOKUP(C21, [1]VT!C:H, 6, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="6">
         <f>VLOOKUP(C21, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="2">
         <v>30</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <v>1</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
         <v>40</v>
       </c>
-      <c r="M21" s="2">
+      <c r="N21" s="2">
         <v>45</v>
       </c>
-      <c r="N21" s="2">
+      <c r="O21" s="2">
         <v>2</v>
       </c>
-      <c r="O21" s="2">
+      <c r="P21" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>46025</v>
       </c>
@@ -7793,41 +10689,45 @@
       <c r="C22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="6" t="e">
+        <f>VLOOKUP(C22, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" s="6">
         <f>VLOOKUP(C22, [1]VT!C:G, 5, FALSE)</f>
         <v>104</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F22" s="6">
         <f>VLOOKUP(C22, [1]VT!C:H, 6, FALSE)</f>
         <v>520</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="6">
         <f>VLOOKUP(C22, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <v>55</v>
       </c>
-      <c r="M22" s="2">
+      <c r="N22" s="2">
         <v>696</v>
       </c>
-      <c r="N22" s="2">
+      <c r="O22" s="2">
         <v>50</v>
       </c>
-      <c r="O22" s="2">
+      <c r="P22" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>46025</v>
       </c>
@@ -7837,47 +10737,51 @@
       <c r="C23" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="6" t="e">
+        <f>VLOOKUP(C23, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E23" s="6">
         <f>VLOOKUP(C23, [1]VT!C:G, 5, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="E23" s="6">
+      <c r="F23" s="6">
         <f>VLOOKUP(C23, [1]VT!C:H, 6, FALSE)</f>
         <v>160</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="6">
         <f>VLOOKUP(C23, [1]VT!C:I, 7, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="2">
         <v>90</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="2">
         <v>1</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
         <v>160</v>
       </c>
-      <c r="M23" s="2">
+      <c r="N23" s="2">
         <v>93</v>
       </c>
-      <c r="N23" s="2">
+      <c r="O23" s="2">
         <v>5</v>
       </c>
-      <c r="O23" s="2">
+      <c r="P23" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>46025</v>
       </c>
@@ -7887,47 +10791,51 @@
       <c r="C24" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="6" t="str">
+        <f>VLOOKUP(C24, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E24" s="6">
         <f>VLOOKUP(C24, [1]VT!C:G, 5, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="E24" s="6">
+      <c r="F24" s="6">
         <f>VLOOKUP(C24, [1]VT!C:H, 6, FALSE)</f>
         <v>160</v>
       </c>
-      <c r="F24" s="6">
+      <c r="G24" s="6">
         <f>VLOOKUP(C24, [1]VT!C:I, 7, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="2">
         <v>80</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <v>3</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
         <v>480</v>
       </c>
-      <c r="M24" s="2">
+      <c r="N24" s="2">
         <v>690</v>
       </c>
-      <c r="N24" s="2">
+      <c r="O24" s="2">
         <v>30</v>
       </c>
-      <c r="O24" s="2">
+      <c r="P24" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>46025</v>
       </c>
@@ -7937,47 +10845,51 @@
       <c r="C25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="6" t="str">
+        <f>VLOOKUP(C25, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E25" s="6">
         <f>VLOOKUP(C25, [1]VT!C:G, 5, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="E25" s="6">
+      <c r="F25" s="6">
         <f>VLOOKUP(C25, [1]VT!C:H, 6, FALSE)</f>
         <v>160</v>
       </c>
-      <c r="F25" s="6">
+      <c r="G25" s="6">
         <f>VLOOKUP(C25, [1]VT!C:I, 7, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="2">
         <v>80</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="2">
         <v>6</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
         <v>780</v>
       </c>
-      <c r="M25" s="2">
+      <c r="N25" s="2">
         <v>784</v>
       </c>
-      <c r="N25" s="2">
+      <c r="O25" s="2">
         <v>38</v>
       </c>
-      <c r="O25" s="2">
+      <c r="P25" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>46026</v>
       </c>
@@ -7987,47 +10899,51 @@
       <c r="C26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="6" t="str">
+        <f>VLOOKUP(C26, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E26" s="6">
         <f>VLOOKUP(C26, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E26" s="6">
+      <c r="F26" s="6">
         <f>VLOOKUP(C26, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F26" s="6">
+      <c r="G26" s="6">
         <f>VLOOKUP(C26, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="2">
         <v>100</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="2">
         <v>4</v>
       </c>
-      <c r="L26" s="2">
+      <c r="M26" s="2">
         <v>160</v>
       </c>
-      <c r="M26" s="2">
+      <c r="N26" s="2">
         <v>340</v>
       </c>
-      <c r="N26" s="2">
+      <c r="O26" s="2">
         <v>10</v>
       </c>
-      <c r="O26" s="2">
+      <c r="P26" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>46026</v>
       </c>
@@ -8037,47 +10953,51 @@
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="6" t="str">
+        <f>VLOOKUP(C27, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E27" s="6">
         <f>VLOOKUP(C27, [1]VT!C:G, 5, FALSE)</f>
         <v>15</v>
       </c>
-      <c r="E27" s="6">
+      <c r="F27" s="6">
         <f>VLOOKUP(C27, [1]VT!C:H, 6, FALSE)</f>
         <v>90</v>
       </c>
-      <c r="F27" s="6">
+      <c r="G27" s="6">
         <f>VLOOKUP(C27, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J27" s="2">
+      <c r="K27" s="2">
         <v>90</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="2">
         <v>4</v>
       </c>
-      <c r="L27" s="2">
+      <c r="M27" s="2">
         <v>512</v>
       </c>
-      <c r="M27" s="2">
+      <c r="N27" s="2">
         <v>449</v>
       </c>
-      <c r="N27" s="2">
+      <c r="O27" s="2">
         <v>11</v>
       </c>
-      <c r="O27" s="2">
+      <c r="P27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>46026</v>
       </c>
@@ -8087,47 +11007,51 @@
       <c r="C28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="6" t="str">
+        <f>VLOOKUP(C28, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E28" s="6">
         <f>VLOOKUP(C28, [1]VT!C:G, 5, FALSE)</f>
         <v>15</v>
       </c>
-      <c r="E28" s="6">
+      <c r="F28" s="6">
         <f>VLOOKUP(C28, [1]VT!C:H, 6, FALSE)</f>
         <v>90</v>
       </c>
-      <c r="F28" s="6">
+      <c r="G28" s="6">
         <f>VLOOKUP(C28, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J28" s="2">
+      <c r="K28" s="2">
         <v>90</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="2">
         <v>3</v>
       </c>
-      <c r="L28" s="2">
+      <c r="M28" s="2">
         <v>384</v>
       </c>
-      <c r="M28" s="2">
+      <c r="N28" s="2">
         <v>358</v>
       </c>
-      <c r="N28" s="2">
+      <c r="O28" s="2">
         <v>12</v>
       </c>
-      <c r="O28" s="2">
+      <c r="P28" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>46026</v>
       </c>
@@ -8137,47 +11061,51 @@
       <c r="C29" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="6" t="e">
+        <f>VLOOKUP(C29, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E29" s="6">
         <f>VLOOKUP(C29, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E29" s="6">
+      <c r="F29" s="6">
         <f>VLOOKUP(C29, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F29" s="6">
+      <c r="G29" s="6">
         <f>VLOOKUP(C29, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" s="2">
         <v>140</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="2">
         <v>3</v>
       </c>
-      <c r="L29" s="2">
+      <c r="M29" s="2">
         <v>576</v>
       </c>
-      <c r="M29" s="2">
+      <c r="N29" s="2">
         <v>476</v>
       </c>
-      <c r="N29" s="2">
+      <c r="O29" s="2">
         <v>32</v>
       </c>
-      <c r="O29" s="2">
+      <c r="P29" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>46026</v>
       </c>
@@ -8187,47 +11115,51 @@
       <c r="C30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="6" t="str">
+        <f>VLOOKUP(C30, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E30" s="6">
         <f>VLOOKUP(C30, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E30" s="6">
+      <c r="F30" s="6">
         <f>VLOOKUP(C30, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F30" s="6">
+      <c r="G30" s="6">
         <f>VLOOKUP(C30, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="2">
         <v>80</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="2">
         <v>11</v>
       </c>
-      <c r="L30" s="2">
+      <c r="M30" s="2">
         <v>880</v>
       </c>
-      <c r="M30" s="2">
+      <c r="N30" s="2">
         <v>316</v>
       </c>
-      <c r="N30" s="2">
+      <c r="O30" s="2">
         <v>40</v>
       </c>
-      <c r="O30" s="2">
+      <c r="P30" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>46026</v>
       </c>
@@ -8237,47 +11169,51 @@
       <c r="C31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="6" t="str">
+        <f>VLOOKUP(C31, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E31" s="6">
         <f>VLOOKUP(C31, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E31" s="6">
+      <c r="F31" s="6">
         <f>VLOOKUP(C31, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F31" s="6">
+      <c r="G31" s="6">
         <f>VLOOKUP(C31, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="2">
         <v>80</v>
       </c>
-      <c r="K31" s="2">
+      <c r="L31" s="2">
         <v>11</v>
       </c>
-      <c r="L31" s="2">
+      <c r="M31" s="2">
         <v>880</v>
       </c>
-      <c r="M31" s="2">
+      <c r="N31" s="2">
         <v>822</v>
       </c>
-      <c r="N31" s="2">
+      <c r="O31" s="2">
         <v>28</v>
       </c>
-      <c r="O31" s="2">
+      <c r="P31" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>46026</v>
       </c>
@@ -8287,47 +11223,51 @@
       <c r="C32" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="6" t="e">
+        <f>VLOOKUP(C32, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E32" s="6">
         <f>VLOOKUP(C32, [1]VT!C:G, 5, FALSE)</f>
         <v>104</v>
       </c>
-      <c r="E32" s="6">
+      <c r="F32" s="6">
         <f>VLOOKUP(C32, [1]VT!C:H, 6, FALSE)</f>
         <v>520</v>
       </c>
-      <c r="F32" s="6">
+      <c r="G32" s="6">
         <f>VLOOKUP(C32, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J32" s="2">
+      <c r="K32" s="2">
         <v>120</v>
       </c>
-      <c r="K32" s="2">
+      <c r="L32" s="2">
         <v>1</v>
       </c>
-      <c r="L32" s="2">
+      <c r="M32" s="2">
         <v>540</v>
       </c>
-      <c r="M32" s="2">
+      <c r="N32" s="2">
         <v>384</v>
       </c>
-      <c r="N32" s="2">
+      <c r="O32" s="2">
         <v>30</v>
       </c>
-      <c r="O32" s="2">
+      <c r="P32" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>46026</v>
       </c>
@@ -8337,47 +11277,51 @@
       <c r="C33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="6" t="str">
+        <f>VLOOKUP(C33, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E33" s="6">
         <f>VLOOKUP(C33, [1]VT!C:G, 5, FALSE)</f>
         <v>72</v>
       </c>
-      <c r="E33" s="6">
+      <c r="F33" s="6">
         <f>VLOOKUP(C33, [1]VT!C:H, 6, FALSE)</f>
         <v>288</v>
       </c>
-      <c r="F33" s="6">
+      <c r="G33" s="6">
         <f>VLOOKUP(C33, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="2">
         <v>40</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="2">
         <v>1</v>
       </c>
-      <c r="L33" s="2">
+      <c r="M33" s="2">
         <v>288</v>
       </c>
-      <c r="M33" s="2">
+      <c r="N33" s="2">
         <v>244</v>
       </c>
-      <c r="N33" s="2">
+      <c r="O33" s="2">
         <v>8</v>
       </c>
-      <c r="O33" s="2">
+      <c r="P33" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>46026</v>
       </c>
@@ -8387,47 +11331,51 @@
       <c r="C34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="6" t="str">
+        <f>VLOOKUP(C34, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E34" s="6">
         <f>VLOOKUP(C34, [1]VT!C:G, 5, FALSE)</f>
         <v>72</v>
       </c>
-      <c r="E34" s="6">
+      <c r="F34" s="6">
         <f>VLOOKUP(C34, [1]VT!C:H, 6, FALSE)</f>
         <v>288</v>
       </c>
-      <c r="F34" s="6">
+      <c r="G34" s="6">
         <f>VLOOKUP(C34, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="H34" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" s="2">
         <v>46</v>
       </c>
-      <c r="K34" s="2">
+      <c r="L34" s="2">
         <v>1</v>
       </c>
-      <c r="L34" s="2">
+      <c r="M34" s="2">
         <v>284</v>
       </c>
-      <c r="M34" s="2">
+      <c r="N34" s="2">
         <v>248</v>
       </c>
-      <c r="N34" s="2">
+      <c r="O34" s="2">
         <v>12</v>
       </c>
-      <c r="O34" s="2">
+      <c r="P34" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>46026</v>
       </c>
@@ -8437,47 +11385,51 @@
       <c r="C35" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="6" t="str">
+        <f>VLOOKUP(C35, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E35" s="6">
         <f>VLOOKUP(C35, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E35" s="6">
+      <c r="F35" s="6">
         <f>VLOOKUP(C35, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F35" s="6">
+      <c r="G35" s="6">
         <f>VLOOKUP(C35, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" s="2">
         <v>60</v>
       </c>
-      <c r="K35" s="2">
+      <c r="L35" s="2">
         <v>6</v>
       </c>
-      <c r="L35" s="2">
+      <c r="M35" s="2">
         <v>240</v>
       </c>
-      <c r="M35" s="2">
+      <c r="N35" s="2">
         <v>271</v>
       </c>
-      <c r="N35" s="2">
+      <c r="O35" s="2">
         <v>9</v>
       </c>
-      <c r="O35" s="2">
+      <c r="P35" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>46026</v>
       </c>
@@ -8487,47 +11439,51 @@
       <c r="C36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="6" t="str">
+        <f>VLOOKUP(C36, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E36" s="6">
         <f>VLOOKUP(C36, [1]VT!C:G, 5, FALSE)</f>
         <v>16</v>
       </c>
-      <c r="E36" s="6">
+      <c r="F36" s="6">
         <f>VLOOKUP(C36, [1]VT!C:H, 6, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="F36" s="6">
+      <c r="G36" s="6">
         <f>VLOOKUP(C36, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" s="2">
         <v>80</v>
       </c>
-      <c r="K36" s="2">
+      <c r="L36" s="2">
         <v>12</v>
       </c>
-      <c r="L36" s="2">
+      <c r="M36" s="2">
         <v>960</v>
       </c>
-      <c r="M36" s="2">
+      <c r="N36" s="2">
         <v>887</v>
       </c>
-      <c r="N36" s="2">
+      <c r="O36" s="2">
         <v>20</v>
       </c>
-      <c r="O36" s="2">
+      <c r="P36" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>46026</v>
       </c>
@@ -8537,47 +11493,51 @@
       <c r="C37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="6" t="str">
+        <f>VLOOKUP(C37, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E37" s="6">
         <f>VLOOKUP(C37, [1]VT!C:G, 5, FALSE)</f>
         <v>16</v>
       </c>
-      <c r="E37" s="6">
+      <c r="F37" s="6">
         <f>VLOOKUP(C37, [1]VT!C:H, 6, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="F37" s="6">
+      <c r="G37" s="6">
         <f>VLOOKUP(C37, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="2">
         <v>80</v>
       </c>
-      <c r="K37" s="2">
+      <c r="L37" s="2">
         <v>12</v>
       </c>
-      <c r="L37" s="2">
+      <c r="M37" s="2">
         <v>960</v>
       </c>
-      <c r="M37" s="2">
+      <c r="N37" s="2">
         <v>842</v>
       </c>
-      <c r="N37" s="2">
+      <c r="O37" s="2">
         <v>22</v>
       </c>
-      <c r="O37" s="2">
+      <c r="P37" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46027</v>
       </c>
@@ -8587,47 +11547,51 @@
       <c r="C38" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="6" t="e">
+        <f>VLOOKUP(C38, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E38" s="6">
         <f>VLOOKUP(C38, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E38" s="6">
+      <c r="F38" s="6">
         <f>VLOOKUP(C38, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F38" s="6">
+      <c r="G38" s="6">
         <f>VLOOKUP(C38, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="H38" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K38" s="2">
         <v>140</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>2</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>384</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>656</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>10</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46027</v>
       </c>
@@ -8637,47 +11601,51 @@
       <c r="C39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="6" t="str">
+        <f>VLOOKUP(C39, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Brown</v>
+      </c>
+      <c r="E39" s="6">
         <f>VLOOKUP(C39, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E39" s="6">
+      <c r="F39" s="6">
         <f>VLOOKUP(C39, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F39" s="6">
+      <c r="G39" s="6">
         <f>VLOOKUP(C39, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="H39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="I39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="J39" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J39" s="2">
+      <c r="K39" s="2">
         <v>140</v>
       </c>
-      <c r="K39" s="2">
+      <c r="L39" s="2">
         <v>2</v>
       </c>
-      <c r="L39" s="2">
+      <c r="M39" s="2">
         <v>384</v>
       </c>
-      <c r="M39" s="2">
+      <c r="N39" s="2">
         <v>424</v>
-      </c>
-      <c r="N39" s="2">
-        <v>0</v>
       </c>
       <c r="O39" s="2">
         <v>0</v>
       </c>
+      <c r="P39" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>46027</v>
       </c>
@@ -8687,47 +11655,51 @@
       <c r="C40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="6" t="str">
+        <f>VLOOKUP(C40, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Brown</v>
+      </c>
+      <c r="E40" s="6">
         <f>VLOOKUP(C40, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E40" s="6">
+      <c r="F40" s="6">
         <f>VLOOKUP(C40, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F40" s="6">
+      <c r="G40" s="6">
         <f>VLOOKUP(C40, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K40" s="2">
         <v>140</v>
       </c>
-      <c r="K40" s="2">
+      <c r="L40" s="2">
         <v>7</v>
       </c>
-      <c r="L40" s="2">
+      <c r="M40" s="2">
         <v>1344</v>
       </c>
-      <c r="M40" s="2">
+      <c r="N40" s="2">
         <v>1254</v>
       </c>
-      <c r="N40" s="2">
+      <c r="O40" s="2">
         <v>23</v>
       </c>
-      <c r="O40" s="2">
+      <c r="P40" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>46027</v>
       </c>
@@ -8738,46 +11710,50 @@
         <v>72</v>
       </c>
       <c r="D41" s="6" t="e">
+        <f>VLOOKUP(C41, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E41" s="6" t="e">
         <f>VLOOKUP(C41, [1]VT!C:G, 5, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E41" s="6" t="e">
+      <c r="F41" s="6" t="e">
         <f>VLOOKUP(C41, [1]VT!C:H, 6, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="F41" s="6" t="e">
+      <c r="G41" s="6" t="e">
         <f>VLOOKUP(C41, [1]VT!C:I, 7, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="H41" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K41" s="2">
         <v>140</v>
       </c>
-      <c r="K41" s="2">
+      <c r="L41" s="2">
         <v>1</v>
       </c>
-      <c r="L41" s="2">
+      <c r="M41" s="2">
         <v>192</v>
       </c>
-      <c r="M41" s="2">
+      <c r="N41" s="2">
         <v>154</v>
       </c>
-      <c r="N41" s="2">
+      <c r="O41" s="2">
         <v>4</v>
       </c>
-      <c r="O41" s="2">
+      <c r="P41" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>46027</v>
       </c>
@@ -8787,47 +11763,51 @@
       <c r="C42" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="6" t="str">
+        <f>VLOOKUP(C42, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E42" s="6">
         <f>VLOOKUP(C42, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E42" s="6">
+      <c r="F42" s="6">
         <f>VLOOKUP(C42, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F42" s="6">
+      <c r="G42" s="6">
         <f>VLOOKUP(C42, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" s="2">
         <v>80</v>
       </c>
-      <c r="K42" s="2">
+      <c r="L42" s="2">
         <v>3</v>
       </c>
-      <c r="L42" s="2">
+      <c r="M42" s="2">
         <v>240</v>
       </c>
-      <c r="M42" s="2">
+      <c r="N42" s="2">
         <v>769</v>
       </c>
-      <c r="N42" s="2">
+      <c r="O42" s="2">
         <v>20</v>
       </c>
-      <c r="O42" s="2">
+      <c r="P42" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>46027</v>
       </c>
@@ -8837,47 +11817,51 @@
       <c r="C43" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="6" t="str">
+        <f>VLOOKUP(C43, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E43" s="6">
         <f>VLOOKUP(C43, [1]VT!C:G, 5, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="E43" s="6">
+      <c r="F43" s="6">
         <f>VLOOKUP(C43, [1]VT!C:H, 6, FALSE)</f>
         <v>200</v>
       </c>
-      <c r="F43" s="6">
+      <c r="G43" s="6">
         <f>VLOOKUP(C43, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="H43" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K43" s="2">
         <v>140</v>
       </c>
-      <c r="K43" s="2">
+      <c r="L43" s="2">
         <v>7</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="2">
         <v>1400</v>
       </c>
-      <c r="M43" s="2">
+      <c r="N43" s="2">
         <v>1435</v>
       </c>
-      <c r="N43" s="2">
+      <c r="O43" s="2">
         <v>31</v>
       </c>
-      <c r="O43" s="2">
+      <c r="P43" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>46027</v>
       </c>
@@ -8887,47 +11871,51 @@
       <c r="C44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="6" t="str">
+        <f>VLOOKUP(C44, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E44" s="6">
         <f>VLOOKUP(C44, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E44" s="6">
+      <c r="F44" s="6">
         <f>VLOOKUP(C44, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F44" s="6">
+      <c r="G44" s="6">
         <f>VLOOKUP(C44, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K44" s="2">
         <v>60</v>
       </c>
-      <c r="K44" s="2">
+      <c r="L44" s="2">
         <v>5</v>
       </c>
-      <c r="L44" s="2">
+      <c r="M44" s="2">
         <v>200</v>
       </c>
-      <c r="M44" s="2">
+      <c r="N44" s="2">
         <v>365</v>
       </c>
-      <c r="N44" s="2">
+      <c r="O44" s="2">
         <v>15</v>
       </c>
-      <c r="O44" s="2">
+      <c r="P44" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>46027</v>
       </c>
@@ -8937,47 +11925,51 @@
       <c r="C45" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="6" t="str">
+        <f>VLOOKUP(C45, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E45" s="6">
         <f>VLOOKUP(C45, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E45" s="6">
+      <c r="F45" s="6">
         <f>VLOOKUP(C45, [1]VT!C:H, 6, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="F45" s="6">
+      <c r="G45" s="6">
         <f>VLOOKUP(C45, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K45" s="2">
         <v>56</v>
       </c>
-      <c r="K45" s="2">
+      <c r="L45" s="2">
         <v>5</v>
       </c>
-      <c r="L45" s="2">
+      <c r="M45" s="2">
         <v>200</v>
       </c>
-      <c r="M45" s="2">
+      <c r="N45" s="2">
         <v>250</v>
       </c>
-      <c r="N45" s="2">
+      <c r="O45" s="2">
         <v>20</v>
       </c>
-      <c r="O45" s="2">
+      <c r="P45" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>46027</v>
       </c>
@@ -8987,47 +11979,51 @@
       <c r="C46" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="6" t="str">
+        <f>VLOOKUP(C46, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E46" s="6">
         <f>VLOOKUP(C46, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E46" s="6">
+      <c r="F46" s="6">
         <f>VLOOKUP(C46, [1]VT!C:H, 6, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="F46" s="6">
+      <c r="G46" s="6">
         <f>VLOOKUP(C46, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K46" s="2">
         <v>56</v>
       </c>
-      <c r="K46" s="2">
+      <c r="L46" s="2">
         <v>4</v>
       </c>
-      <c r="L46" s="2">
+      <c r="M46" s="2">
         <v>360</v>
       </c>
-      <c r="M46" s="2">
+      <c r="N46" s="2">
         <v>382</v>
       </c>
-      <c r="N46" s="2">
+      <c r="O46" s="2">
         <v>10</v>
       </c>
-      <c r="O46" s="2">
+      <c r="P46" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46027</v>
       </c>
@@ -9037,47 +12033,51 @@
       <c r="C47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="6" t="str">
+        <f>VLOOKUP(C47, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E47" s="6">
         <f>VLOOKUP(C47, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E47" s="6">
+      <c r="F47" s="6">
         <f>VLOOKUP(C47, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F47" s="6">
+      <c r="G47" s="6">
         <f>VLOOKUP(C47, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H47" s="8">
+      <c r="I47" s="8">
         <v>46053</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="J47" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J47" s="2">
+      <c r="K47" s="2">
         <v>115</v>
       </c>
-      <c r="K47" s="2">
+      <c r="L47" s="2">
         <v>2</v>
       </c>
-      <c r="L47" s="2">
+      <c r="M47" s="2">
         <v>80</v>
       </c>
-      <c r="M47" s="2">
+      <c r="N47" s="2">
         <v>75</v>
       </c>
-      <c r="N47" s="2">
+      <c r="O47" s="2">
         <v>8</v>
       </c>
-      <c r="O47" s="2">
+      <c r="P47" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>46027</v>
       </c>
@@ -9087,47 +12087,51 @@
       <c r="C48" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="6" t="str">
+        <f>VLOOKUP(C48, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E48" s="6">
         <f>VLOOKUP(C48, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E48" s="6">
+      <c r="F48" s="6">
         <f>VLOOKUP(C48, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F48" s="6">
+      <c r="G48" s="6">
         <f>VLOOKUP(C48, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="J48" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J48" s="2">
+      <c r="K48" s="2">
         <v>95</v>
       </c>
-      <c r="K48" s="2">
+      <c r="L48" s="2">
         <v>4</v>
       </c>
-      <c r="L48" s="2">
+      <c r="M48" s="2">
         <v>320</v>
       </c>
-      <c r="M48" s="2">
+      <c r="N48" s="2">
         <v>158</v>
       </c>
-      <c r="N48" s="2">
+      <c r="O48" s="2">
         <v>16</v>
       </c>
-      <c r="O48" s="2">
+      <c r="P48" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>46027</v>
       </c>
@@ -9137,47 +12141,51 @@
       <c r="C49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="6" t="str">
+        <f>VLOOKUP(C49, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E49" s="6">
         <f>VLOOKUP(C49, [1]VT!C:G, 5, FALSE)</f>
         <v>16</v>
       </c>
-      <c r="E49" s="6">
+      <c r="F49" s="6">
         <f>VLOOKUP(C49, [1]VT!C:H, 6, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="F49" s="6">
+      <c r="G49" s="6">
         <f>VLOOKUP(C49, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="H49" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" s="2">
         <v>80</v>
       </c>
-      <c r="K49" s="2">
+      <c r="L49" s="2">
         <v>5</v>
       </c>
-      <c r="L49" s="2">
+      <c r="M49" s="2">
         <v>400</v>
       </c>
-      <c r="M49" s="2">
+      <c r="N49" s="2">
         <v>498</v>
       </c>
-      <c r="N49" s="2">
+      <c r="O49" s="2">
         <v>20</v>
       </c>
-      <c r="O49" s="2">
+      <c r="P49" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>46027</v>
       </c>
@@ -9187,47 +12195,51 @@
       <c r="C50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="6" t="str">
+        <f>VLOOKUP(C50, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E50" s="6">
         <f>VLOOKUP(C50, [1]VT!C:G, 5, FALSE)</f>
         <v>15</v>
       </c>
-      <c r="E50" s="6">
+      <c r="F50" s="6">
         <f>VLOOKUP(C50, [1]VT!C:H, 6, FALSE)</f>
         <v>90</v>
       </c>
-      <c r="F50" s="6">
+      <c r="G50" s="6">
         <f>VLOOKUP(C50, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="H50" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K50" s="2">
         <v>100</v>
       </c>
-      <c r="K50" s="2">
+      <c r="L50" s="2">
         <v>4</v>
       </c>
-      <c r="L50" s="2">
+      <c r="M50" s="2">
         <v>512</v>
       </c>
-      <c r="M50" s="2">
+      <c r="N50" s="2">
         <v>396</v>
       </c>
-      <c r="N50" s="2">
+      <c r="O50" s="2">
         <v>20</v>
       </c>
-      <c r="O50" s="2">
+      <c r="P50" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>46028</v>
       </c>
@@ -9238,46 +12250,50 @@
         <v>72</v>
       </c>
       <c r="D51" s="6" t="e">
+        <f>VLOOKUP(C51, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E51" s="6" t="e">
         <f>VLOOKUP(C51, [1]VT!C:G, 5, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E51" s="6" t="e">
+      <c r="F51" s="6" t="e">
         <f>VLOOKUP(C51, [1]VT!C:H, 6, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="F51" s="6" t="e">
+      <c r="G51" s="6" t="e">
         <f>VLOOKUP(C51, [1]VT!C:I, 7, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="H51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="I51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="J51" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J51" s="2">
+      <c r="K51" s="2">
         <v>140</v>
       </c>
-      <c r="K51" s="2">
+      <c r="L51" s="2">
         <v>2</v>
       </c>
-      <c r="L51" s="2">
+      <c r="M51" s="2">
         <v>384</v>
       </c>
-      <c r="M51" s="2">
+      <c r="N51" s="2">
         <v>221</v>
       </c>
-      <c r="N51" s="2">
+      <c r="O51" s="2">
         <v>31</v>
       </c>
-      <c r="O51" s="2">
+      <c r="P51" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>46028</v>
       </c>
@@ -9287,47 +12303,51 @@
       <c r="C52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="6" t="str">
+        <f>VLOOKUP(C52, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E52" s="6">
         <f>VLOOKUP(C52, [1]VT!C:G, 5, FALSE)</f>
         <v>78</v>
       </c>
-      <c r="E52" s="6">
+      <c r="F52" s="6">
         <f>VLOOKUP(C52, [1]VT!C:H, 6, FALSE)</f>
         <v>234</v>
       </c>
-      <c r="F52" s="6">
+      <c r="G52" s="6">
         <f>VLOOKUP(C52, [1]VT!C:I, 7, FALSE)</f>
         <v>3</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="H52" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K52" s="2">
         <v>150</v>
       </c>
-      <c r="K52" s="2">
+      <c r="L52" s="2">
         <v>4</v>
       </c>
-      <c r="L52" s="2">
+      <c r="M52" s="2">
         <v>512</v>
       </c>
-      <c r="M52" s="2">
+      <c r="N52" s="2">
         <v>467</v>
       </c>
-      <c r="N52" s="2">
+      <c r="O52" s="2">
         <v>7</v>
       </c>
-      <c r="O52" s="2">
+      <c r="P52" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>46028</v>
       </c>
@@ -9337,47 +12357,51 @@
       <c r="C53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="6" t="str">
+        <f>VLOOKUP(C53, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E53" s="6">
         <f>VLOOKUP(C53, [1]VT!C:G, 5, FALSE)</f>
         <v>78</v>
       </c>
-      <c r="E53" s="6">
+      <c r="F53" s="6">
         <f>VLOOKUP(C53, [1]VT!C:H, 6, FALSE)</f>
         <v>234</v>
       </c>
-      <c r="F53" s="6">
+      <c r="G53" s="6">
         <f>VLOOKUP(C53, [1]VT!C:I, 7, FALSE)</f>
         <v>3</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="H53" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K53" s="2">
         <v>150</v>
       </c>
-      <c r="K53" s="2">
+      <c r="L53" s="2">
         <v>6</v>
       </c>
-      <c r="L53" s="2">
+      <c r="M53" s="2">
         <v>768</v>
       </c>
-      <c r="M53" s="2">
+      <c r="N53" s="2">
         <v>760</v>
       </c>
-      <c r="N53" s="2">
+      <c r="O53" s="2">
         <v>12</v>
       </c>
-      <c r="O53" s="2">
+      <c r="P53" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>46028</v>
       </c>
@@ -9387,47 +12411,51 @@
       <c r="C54" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="6" t="str">
+        <f>VLOOKUP(C54, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E54" s="6">
         <f>VLOOKUP(C54, [1]VT!C:G, 5, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="E54" s="6">
+      <c r="F54" s="6">
         <f>VLOOKUP(C54, [1]VT!C:H, 6, FALSE)</f>
         <v>384</v>
       </c>
-      <c r="F54" s="6">
+      <c r="G54" s="6">
         <f>VLOOKUP(C54, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="H54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="I54" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I54" s="2" t="s">
+      <c r="J54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J54" s="2">
+      <c r="K54" s="2">
         <v>80</v>
       </c>
-      <c r="K54" s="2">
+      <c r="L54" s="2">
         <v>3</v>
       </c>
-      <c r="L54" s="2">
+      <c r="M54" s="2">
         <v>576</v>
       </c>
-      <c r="M54" s="2">
+      <c r="N54" s="2">
         <v>299</v>
       </c>
-      <c r="N54" s="2">
+      <c r="O54" s="2">
         <v>12</v>
       </c>
-      <c r="O54" s="2">
+      <c r="P54" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>46028</v>
       </c>
@@ -9437,44 +12465,48 @@
       <c r="C55" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="6" t="str">
+        <f>VLOOKUP(C55, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E55" s="6">
         <f>VLOOKUP(C55, [1]VT!C:G, 5, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="E55" s="6">
+      <c r="F55" s="6">
         <f>VLOOKUP(C55, [1]VT!C:H, 6, FALSE)</f>
         <v>200</v>
       </c>
-      <c r="F55" s="6">
+      <c r="G55" s="6">
         <f>VLOOKUP(C55, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="H55" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K55" s="2">
         <v>140</v>
       </c>
-      <c r="K55" s="2">
+      <c r="L55" s="2">
         <v>3</v>
       </c>
-      <c r="L55" s="2">
+      <c r="M55" s="2">
         <v>600</v>
       </c>
-      <c r="M55" s="2">
+      <c r="N55" s="2">
         <v>166</v>
       </c>
-      <c r="N55" s="2">
+      <c r="O55" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>46028</v>
       </c>
@@ -9484,47 +12516,51 @@
       <c r="C56" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="6" t="str">
+        <f>VLOOKUP(C56, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E56" s="6">
         <f>VLOOKUP(C56, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E56" s="6">
+      <c r="F56" s="6">
         <f>VLOOKUP(C56, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F56" s="6">
+      <c r="G56" s="6">
         <f>VLOOKUP(C56, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="H56" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H56" s="8">
-        <v>46053</v>
       </c>
       <c r="I56" s="8">
         <v>46053</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="8">
+        <v>46053</v>
+      </c>
+      <c r="K56" s="2">
         <v>115</v>
       </c>
-      <c r="K56" s="2">
+      <c r="L56" s="2">
         <v>20</v>
       </c>
-      <c r="L56" s="2">
+      <c r="M56" s="2">
         <v>800</v>
       </c>
-      <c r="M56" s="2">
+      <c r="N56" s="2">
         <v>747</v>
       </c>
-      <c r="N56" s="2">
+      <c r="O56" s="2">
         <v>18</v>
       </c>
-      <c r="O56" s="2">
+      <c r="P56" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>46028</v>
       </c>
@@ -9534,47 +12570,51 @@
       <c r="C57" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="6" t="str">
+        <f>VLOOKUP(C57, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E57" s="6">
         <f>VLOOKUP(C57, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E57" s="6">
+      <c r="F57" s="6">
         <f>VLOOKUP(C57, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F57" s="6">
+      <c r="G57" s="6">
         <f>VLOOKUP(C57, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="H57" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H57" s="8">
-        <v>46053</v>
       </c>
       <c r="I57" s="8">
         <v>46053</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57" s="8">
+        <v>46053</v>
+      </c>
+      <c r="K57" s="2">
         <v>115</v>
       </c>
-      <c r="K57" s="2">
+      <c r="L57" s="2">
         <v>9</v>
       </c>
-      <c r="L57" s="2">
+      <c r="M57" s="2">
         <v>720</v>
       </c>
-      <c r="M57" s="2">
+      <c r="N57" s="2">
         <v>692</v>
       </c>
-      <c r="N57" s="2">
+      <c r="O57" s="2">
         <v>41</v>
       </c>
-      <c r="O57" s="2">
+      <c r="P57" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>46028</v>
       </c>
@@ -9584,47 +12624,51 @@
       <c r="C58" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="6" t="str">
+        <f>VLOOKUP(C58, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E58" s="6">
         <f>VLOOKUP(C58, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E58" s="6">
+      <c r="F58" s="6">
         <f>VLOOKUP(C58, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F58" s="6">
+      <c r="G58" s="6">
         <f>VLOOKUP(C58, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K58" s="2">
         <v>95</v>
       </c>
-      <c r="K58" s="2">
+      <c r="L58" s="2">
         <v>11</v>
       </c>
-      <c r="L58" s="2">
+      <c r="M58" s="2">
         <v>880</v>
       </c>
-      <c r="M58" s="2">
+      <c r="N58" s="2">
         <v>979</v>
       </c>
-      <c r="N58" s="2">
+      <c r="O58" s="2">
         <v>40</v>
       </c>
-      <c r="O58" s="2">
+      <c r="P58" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>46028</v>
       </c>
@@ -9634,47 +12678,51 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="6" t="str">
+        <f>VLOOKUP(C59, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E59" s="6">
         <f>VLOOKUP(C59, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E59" s="6">
+      <c r="F59" s="6">
         <f>VLOOKUP(C59, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F59" s="6">
+      <c r="G59" s="6">
         <f>VLOOKUP(C59, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="H59" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K59" s="2">
         <v>95</v>
       </c>
-      <c r="K59" s="2">
+      <c r="L59" s="2">
         <v>5</v>
       </c>
-      <c r="L59" s="2">
+      <c r="M59" s="2">
         <v>400</v>
       </c>
-      <c r="M59" s="2">
+      <c r="N59" s="2">
         <v>382</v>
       </c>
-      <c r="N59" s="2">
+      <c r="O59" s="2">
         <v>11</v>
       </c>
-      <c r="O59" s="2">
+      <c r="P59" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>46028</v>
       </c>
@@ -9684,47 +12732,51 @@
       <c r="C60" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="6" t="e">
+        <f>VLOOKUP(C60, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E60" s="6">
         <f>VLOOKUP(C60, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E60" s="6">
+      <c r="F60" s="6">
         <f>VLOOKUP(C60, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F60" s="6">
+      <c r="G60" s="6">
         <f>VLOOKUP(C60, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="H60" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K60" s="2">
         <v>120</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="L60" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="L60" s="2" t="s">
+      <c r="M60" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M60" s="2">
+      <c r="N60" s="2">
         <v>750</v>
       </c>
-      <c r="N60" s="2">
+      <c r="O60" s="2">
         <v>30</v>
       </c>
-      <c r="O60" s="2">
+      <c r="P60" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>46028</v>
       </c>
@@ -9734,47 +12786,51 @@
       <c r="C61" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="6" t="str">
+        <f>VLOOKUP(C61, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E61" s="6">
         <f>VLOOKUP(C61, [1]VT!C:G, 5, FALSE)</f>
         <v>15</v>
       </c>
-      <c r="E61" s="6">
+      <c r="F61" s="6">
         <f>VLOOKUP(C61, [1]VT!C:H, 6, FALSE)</f>
         <v>90</v>
       </c>
-      <c r="F61" s="6">
+      <c r="G61" s="6">
         <f>VLOOKUP(C61, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="H61" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K61" s="2">
         <v>100</v>
       </c>
-      <c r="K61" s="2">
+      <c r="L61" s="2">
         <v>5</v>
       </c>
-      <c r="L61" s="2">
+      <c r="M61" s="2">
         <v>640</v>
       </c>
-      <c r="M61" s="2">
+      <c r="N61" s="2">
         <v>319</v>
       </c>
-      <c r="N61" s="2">
+      <c r="O61" s="2">
         <v>30</v>
       </c>
-      <c r="O61" s="2">
+      <c r="P61" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>46028</v>
       </c>
@@ -9784,47 +12840,51 @@
       <c r="C62" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="6" t="str">
+        <f>VLOOKUP(C62, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E62" s="6">
         <f>VLOOKUP(C62, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E62" s="6">
+      <c r="F62" s="6">
         <f>VLOOKUP(C62, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F62" s="6">
+      <c r="G62" s="6">
         <f>VLOOKUP(C62, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="H62" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="2">
         <v>100</v>
       </c>
-      <c r="K62" s="2">
+      <c r="L62" s="2">
         <v>20</v>
       </c>
-      <c r="L62" s="2">
+      <c r="M62" s="2">
         <v>800</v>
       </c>
-      <c r="M62" s="2">
+      <c r="N62" s="2">
         <v>740</v>
       </c>
-      <c r="N62" s="2">
+      <c r="O62" s="2">
         <v>10</v>
       </c>
-      <c r="O62" s="2">
+      <c r="P62" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>46028</v>
       </c>
@@ -9834,47 +12894,51 @@
       <c r="C63" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="6" t="str">
+        <f>VLOOKUP(C63, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E63" s="6">
         <f>VLOOKUP(C63, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E63" s="6">
+      <c r="F63" s="6">
         <f>VLOOKUP(C63, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F63" s="6">
+      <c r="G63" s="6">
         <f>VLOOKUP(C63, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="2">
         <v>100</v>
       </c>
-      <c r="K63" s="2">
+      <c r="L63" s="2">
         <v>10</v>
       </c>
-      <c r="L63" s="2">
+      <c r="M63" s="2">
         <v>400</v>
       </c>
-      <c r="M63" s="2">
+      <c r="N63" s="2">
         <v>340</v>
       </c>
-      <c r="N63" s="2">
+      <c r="O63" s="2">
         <v>10</v>
       </c>
-      <c r="O63" s="2">
+      <c r="P63" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>46028</v>
       </c>
@@ -9884,47 +12948,51 @@
       <c r="C64" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="6" t="str">
+        <f>VLOOKUP(C64, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E64" s="6">
         <f>VLOOKUP(C64, [1]VT!C:G, 5, FALSE)</f>
         <v>16</v>
       </c>
-      <c r="E64" s="6">
+      <c r="F64" s="6">
         <f>VLOOKUP(C64, [1]VT!C:H, 6, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="F64" s="6">
+      <c r="G64" s="6">
         <f>VLOOKUP(C64, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="H64" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" s="2">
         <v>80</v>
       </c>
-      <c r="K64" s="2">
+      <c r="L64" s="2">
         <v>8</v>
-      </c>
-      <c r="L64" s="2">
-        <v>640</v>
       </c>
       <c r="M64" s="2">
         <v>640</v>
       </c>
       <c r="N64" s="2">
+        <v>640</v>
+      </c>
+      <c r="O64" s="2">
         <v>10</v>
       </c>
-      <c r="O64" s="2">
+      <c r="P64" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>46029</v>
       </c>
@@ -9934,47 +13002,51 @@
       <c r="C65" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="6" t="str">
+        <f>VLOOKUP(C65, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E65" s="6">
         <f>VLOOKUP(C65, [1]VT!C:G, 5, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="E65" s="6">
+      <c r="F65" s="6">
         <f>VLOOKUP(C65, [1]VT!C:H, 6, FALSE)</f>
         <v>384</v>
       </c>
-      <c r="F65" s="6">
+      <c r="G65" s="6">
         <f>VLOOKUP(C65, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="H65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="I65" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="J65" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J65" s="2">
+      <c r="K65" s="2">
         <v>80</v>
       </c>
-      <c r="K65" s="2">
+      <c r="L65" s="2">
         <v>4</v>
       </c>
-      <c r="L65" s="2">
+      <c r="M65" s="2">
         <v>768</v>
       </c>
-      <c r="M65" s="2">
+      <c r="N65" s="2">
         <v>637</v>
       </c>
-      <c r="N65" s="2">
+      <c r="O65" s="2">
         <v>20</v>
       </c>
-      <c r="O65" s="2">
+      <c r="P65" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>46029</v>
       </c>
@@ -9984,47 +13056,51 @@
       <c r="C66" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="6" t="str">
+        <f>VLOOKUP(C66, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E66" s="6">
         <f>VLOOKUP(C66, [1]VT!C:G, 5, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="E66" s="6">
+      <c r="F66" s="6">
         <f>VLOOKUP(C66, [1]VT!C:H, 6, FALSE)</f>
         <v>384</v>
       </c>
-      <c r="F66" s="6">
+      <c r="G66" s="6">
         <f>VLOOKUP(C66, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="H66" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="I66" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="J66" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J66" s="2">
+      <c r="K66" s="2">
         <v>80</v>
       </c>
-      <c r="K66" s="2">
+      <c r="L66" s="2">
         <v>4</v>
       </c>
-      <c r="L66" s="2">
+      <c r="M66" s="2">
         <v>768</v>
       </c>
-      <c r="M66" s="2">
+      <c r="N66" s="2">
         <v>586</v>
       </c>
-      <c r="N66" s="2">
+      <c r="O66" s="2">
         <v>24</v>
       </c>
-      <c r="O66" s="2">
+      <c r="P66" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>46029</v>
       </c>
@@ -10034,47 +13110,51 @@
       <c r="C67" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="6" t="str">
+        <f>VLOOKUP(C67, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E67" s="6">
         <f>VLOOKUP(C67, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E67" s="6">
+      <c r="F67" s="6">
         <f>VLOOKUP(C67, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F67" s="6">
+      <c r="G67" s="6">
         <f>VLOOKUP(C67, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="H67" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H67" s="8">
-        <v>46053</v>
       </c>
       <c r="I67" s="8">
         <v>46053</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="8">
+        <v>46053</v>
+      </c>
+      <c r="K67" s="2">
         <v>115</v>
       </c>
-      <c r="K67" s="2">
+      <c r="L67" s="2">
         <v>30</v>
       </c>
-      <c r="L67" s="2">
+      <c r="M67" s="2">
         <v>1200</v>
       </c>
-      <c r="M67" s="2">
+      <c r="N67" s="2">
         <v>781</v>
       </c>
-      <c r="N67" s="2">
+      <c r="O67" s="2">
         <v>10</v>
       </c>
-      <c r="O67" s="2">
+      <c r="P67" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>46029</v>
       </c>
@@ -10084,47 +13164,51 @@
       <c r="C68" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="6" t="str">
+        <f>VLOOKUP(C68, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E68" s="6">
         <f>VLOOKUP(C68, [1]VT!C:G, 5, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="E68" s="6">
+      <c r="F68" s="6">
         <f>VLOOKUP(C68, [1]VT!C:H, 6, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="F68" s="6">
+      <c r="G68" s="6">
         <f>VLOOKUP(C68, [1]VT!C:I, 7, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H68" s="8">
-        <v>46053</v>
       </c>
       <c r="I68" s="8">
         <v>46053</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68" s="8">
+        <v>46053</v>
+      </c>
+      <c r="K68" s="2">
         <v>115</v>
       </c>
-      <c r="K68" s="2">
+      <c r="L68" s="2">
         <v>10</v>
       </c>
-      <c r="L68" s="2">
+      <c r="M68" s="2">
         <v>800</v>
       </c>
-      <c r="M68" s="2">
+      <c r="N68" s="2">
         <v>650</v>
       </c>
-      <c r="N68" s="2">
+      <c r="O68" s="2">
         <v>32</v>
       </c>
-      <c r="O68" s="2">
+      <c r="P68" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>46029</v>
       </c>
@@ -10134,47 +13218,51 @@
       <c r="C69" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="6" t="e">
+        <f>VLOOKUP(C69, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E69" s="6">
         <f>VLOOKUP(C69, [1]VT!C:G, 5, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="E69" s="6">
+      <c r="F69" s="6">
         <f>VLOOKUP(C69, [1]VT!C:H, 6, FALSE)</f>
         <v>192</v>
       </c>
-      <c r="F69" s="6">
+      <c r="G69" s="6">
         <f>VLOOKUP(C69, [1]VT!C:I, 7, FALSE)</f>
         <v>6</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="H69" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K69" s="2">
         <v>120</v>
       </c>
-      <c r="K69" s="2">
+      <c r="L69" s="2">
         <v>1</v>
       </c>
-      <c r="L69" s="2">
+      <c r="M69" s="2">
         <v>160</v>
       </c>
-      <c r="M69" s="2">
+      <c r="N69" s="2">
         <v>134</v>
       </c>
-      <c r="N69" s="2">
+      <c r="O69" s="2">
         <v>6</v>
       </c>
-      <c r="O69" s="2">
+      <c r="P69" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>46029</v>
       </c>
@@ -10185,46 +13273,50 @@
         <v>66</v>
       </c>
       <c r="D70" s="6" t="e">
+        <f>VLOOKUP(C70, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E70" s="6" t="e">
         <f>VLOOKUP(C70, [1]VT!C:G, 5, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E70" s="6" t="e">
+      <c r="F70" s="6" t="e">
         <f>VLOOKUP(C70, [1]VT!C:H, 6, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="F70" s="6" t="e">
+      <c r="G70" s="6" t="e">
         <f>VLOOKUP(C70, [1]VT!C:I, 7, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="H70" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K70" s="2">
         <v>46</v>
       </c>
-      <c r="K70" s="2">
+      <c r="L70" s="2">
         <v>1</v>
       </c>
-      <c r="L70" s="2">
+      <c r="M70" s="2">
         <v>288</v>
       </c>
-      <c r="M70" s="2">
+      <c r="N70" s="2">
         <v>421</v>
       </c>
-      <c r="N70" s="2">
+      <c r="O70" s="2">
         <v>17</v>
       </c>
-      <c r="O70" s="2">
+      <c r="P70" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>46029</v>
       </c>
@@ -10235,46 +13327,50 @@
         <v>66</v>
       </c>
       <c r="D71" s="6" t="e">
+        <f>VLOOKUP(C71, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E71" s="6" t="e">
         <f>VLOOKUP(C71, [1]VT!C:G, 5, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="E71" s="6" t="e">
+      <c r="F71" s="6" t="e">
         <f>VLOOKUP(C71, [1]VT!C:H, 6, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="F71" s="6" t="e">
+      <c r="G71" s="6" t="e">
         <f>VLOOKUP(C71, [1]VT!C:I, 7, FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="H71" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K71" s="2">
         <v>46</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M71" s="2">
+      <c r="M71" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N71" s="2">
         <v>240</v>
       </c>
-      <c r="N71" s="2">
+      <c r="O71" s="2">
         <v>12</v>
       </c>
-      <c r="O71" s="2">
+      <c r="P71" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>46029</v>
       </c>
@@ -10284,47 +13380,51 @@
       <c r="C72" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="6" t="str">
+        <f>VLOOKUP(C72, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Black</v>
+      </c>
+      <c r="E72" s="6">
         <f>VLOOKUP(C72, [1]VT!C:G, 5, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="E72" s="6">
+      <c r="F72" s="6">
         <f>VLOOKUP(C72, [1]VT!C:H, 6, FALSE)</f>
         <v>100</v>
       </c>
-      <c r="F72" s="6">
+      <c r="G72" s="6">
         <f>VLOOKUP(C72, [1]VT!C:I, 7, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="H72" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" s="2">
         <v>80</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M72" s="2">
+      <c r="M72" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N72" s="2">
         <v>445</v>
       </c>
-      <c r="N72" s="2">
+      <c r="O72" s="2">
         <v>20</v>
       </c>
-      <c r="O72" s="2">
+      <c r="P72" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>46029</v>
       </c>
@@ -10334,47 +13434,51 @@
       <c r="C73" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="6" t="str">
+        <f>VLOOKUP(C73, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>White</v>
+      </c>
+      <c r="E73" s="6">
         <f>VLOOKUP(C73, [1]VT!C:G, 5, FALSE)</f>
         <v>16</v>
       </c>
-      <c r="E73" s="6">
+      <c r="F73" s="6">
         <f>VLOOKUP(C73, [1]VT!C:H, 6, FALSE)</f>
         <v>64</v>
       </c>
-      <c r="F73" s="6">
+      <c r="G73" s="6">
         <f>VLOOKUP(C73, [1]VT!C:I, 7, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="H73" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J73" s="2">
+      <c r="J73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" s="2">
         <v>80</v>
       </c>
-      <c r="K73" s="2">
+      <c r="L73" s="2">
         <v>10</v>
       </c>
-      <c r="L73" s="2">
+      <c r="M73" s="2">
         <v>800</v>
       </c>
-      <c r="M73" s="2">
+      <c r="N73" s="2">
         <v>486</v>
       </c>
-      <c r="N73" s="2">
+      <c r="O73" s="2">
         <v>14</v>
       </c>
-      <c r="O73" s="2">
+      <c r="P73" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>46029</v>
       </c>
@@ -10384,47 +13488,51 @@
       <c r="C74" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="6" t="str">
+        <f>VLOOKUP(C74, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Blue</v>
+      </c>
+      <c r="E74" s="6">
         <f>VLOOKUP(C74, [1]VT!C:G, 5, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="E74" s="6">
+      <c r="F74" s="6">
         <f>VLOOKUP(C74, [1]VT!C:H, 6, FALSE)</f>
         <v>160</v>
       </c>
-      <c r="F74" s="6">
+      <c r="G74" s="6">
         <f>VLOOKUP(C74, [1]VT!C:I, 7, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="H74" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J74" s="2">
+      <c r="J74" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K74" s="2">
         <v>66</v>
       </c>
-      <c r="K74" s="2">
+      <c r="L74" s="2">
         <v>2</v>
       </c>
-      <c r="L74" s="2">
+      <c r="M74" s="2">
         <v>320</v>
       </c>
-      <c r="M74" s="2">
+      <c r="N74" s="2">
         <v>264</v>
       </c>
-      <c r="N74" s="2">
+      <c r="O74" s="2">
         <v>20</v>
       </c>
-      <c r="O74" s="2">
+      <c r="P74" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>46029</v>
       </c>
@@ -10434,233 +13542,237 @@
       <c r="C75" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="6" t="str">
+        <f>VLOOKUP(C75, '[2]Summery sheet'!B:G, 6, FALSE)</f>
+        <v>Blue</v>
+      </c>
+      <c r="E75" s="6">
         <f>VLOOKUP(C75, [1]VT!C:G, 5, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="E75" s="6">
+      <c r="F75" s="6">
         <f>VLOOKUP(C75, [1]VT!C:H, 6, FALSE)</f>
         <v>160</v>
       </c>
-      <c r="F75" s="6">
+      <c r="G75" s="6">
         <f>VLOOKUP(C75, [1]VT!C:I, 7, FALSE)</f>
         <v>8</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="H75" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J75" s="2">
+      <c r="J75" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K75" s="2">
         <v>66</v>
       </c>
-      <c r="K75" s="2">
+      <c r="L75" s="2">
         <v>5</v>
       </c>
-      <c r="L75" s="2">
+      <c r="M75" s="2">
         <v>800</v>
       </c>
-      <c r="M75" s="2">
+      <c r="N75" s="2">
         <v>722</v>
       </c>
-      <c r="N75" s="2">
+      <c r="O75" s="2">
         <v>14</v>
       </c>
-      <c r="O75" s="2">
+      <c r="P75" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O75">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P75">
     <sortCondition ref="A2:A75"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="193" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2 G2">
-    <cfRule type="duplicateValues" dxfId="192" priority="66"/>
+  <conditionalFormatting sqref="C2 H2">
+    <cfRule type="duplicateValues" dxfId="120" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="191" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="duplicateValues" dxfId="190" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="duplicateValues" dxfId="189" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="duplicateValues" dxfId="188" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="187" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="186" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="185" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="184" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11">
-    <cfRule type="duplicateValues" dxfId="183" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="182" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="duplicateValues" dxfId="181" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="178" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="duplicateValues" dxfId="177" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="175" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20">
-    <cfRule type="duplicateValues" dxfId="174" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21">
-    <cfRule type="duplicateValues" dxfId="173" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="duplicateValues" dxfId="172" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25">
-    <cfRule type="duplicateValues" dxfId="171" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26">
-    <cfRule type="duplicateValues" dxfId="170" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27">
-    <cfRule type="duplicateValues" dxfId="169" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28">
-    <cfRule type="duplicateValues" dxfId="168" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31">
-    <cfRule type="duplicateValues" dxfId="167" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="166" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="165" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35">
-    <cfRule type="duplicateValues" dxfId="164" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36">
-    <cfRule type="duplicateValues" dxfId="163" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37">
-    <cfRule type="duplicateValues" dxfId="162" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38">
-    <cfRule type="duplicateValues" dxfId="161" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="160" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="159" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41">
-    <cfRule type="duplicateValues" dxfId="158" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42">
-    <cfRule type="duplicateValues" dxfId="157" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="156" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="155" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="154" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46">
-    <cfRule type="duplicateValues" dxfId="153" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="152" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
-    <cfRule type="duplicateValues" dxfId="151" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C49">
-    <cfRule type="duplicateValues" dxfId="150" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50">
-    <cfRule type="duplicateValues" dxfId="149" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="147" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55">
-    <cfRule type="duplicateValues" dxfId="146" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C56">
-    <cfRule type="duplicateValues" dxfId="145" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60">
-    <cfRule type="duplicateValues" dxfId="144" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C61">
-    <cfRule type="duplicateValues" dxfId="143" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C57">
-    <cfRule type="duplicateValues" dxfId="142" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C58">
-    <cfRule type="duplicateValues" dxfId="141" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59">
-    <cfRule type="duplicateValues" dxfId="140" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C62">
-    <cfRule type="duplicateValues" dxfId="139" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C63">
-    <cfRule type="duplicateValues" dxfId="138" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68">
-    <cfRule type="duplicateValues" dxfId="137" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69">
-    <cfRule type="duplicateValues" dxfId="136" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C70">
-    <cfRule type="duplicateValues" dxfId="135" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C71">
-    <cfRule type="duplicateValues" dxfId="134" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C72">
-    <cfRule type="duplicateValues" dxfId="133" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="132" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
